--- a/A_Main_Code/Outcome/Results_main.xlsx
+++ b/A_Main_Code/Outcome/Results_main.xlsx
@@ -57,5435 +57,5435 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="true"/>
-    <col min="2" max="2" width="14.453125" customWidth="true"/>
+    <col min="2" max="2" width="14.08984375" customWidth="true"/>
     <col min="3" max="3" width="12.453125" customWidth="true"/>
     <col min="4" max="4" width="12.453125" customWidth="true"/>
-    <col min="5" max="5" width="14.08984375" customWidth="true"/>
+    <col min="5" max="5" width="14.453125" customWidth="true"/>
     <col min="6" max="6" width="12.453125" customWidth="true"/>
-    <col min="7" max="7" width="15.453125" customWidth="true"/>
-    <col min="8" max="8" width="16.08984375" customWidth="true"/>
-    <col min="9" max="9" width="16.08984375" customWidth="true"/>
+    <col min="7" max="7" width="15.7265625" customWidth="true"/>
+    <col min="8" max="8" width="15.453125" customWidth="true"/>
+    <col min="9" max="9" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.19674358982683601</v>
+        <v>0.20023874594077301</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.15448404587162201</v>
+        <v>-0.16782691085974399</v>
       </c>
       <c r="C1" s="0">
-        <v>0.30327980621324002</v>
+        <v>0.28376351646647402</v>
       </c>
       <c r="D1" s="0">
-        <v>0.21319909458949851</v>
+        <v>0.21053756220693509</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.09515343992685299</v>
+        <v>-0.10980589097628934</v>
       </c>
       <c r="F1" s="0">
-        <v>0.29173143875816177</v>
+        <v>0.23649889403965726</v>
       </c>
       <c r="G1" s="0">
-        <v>-0.016332241499836635</v>
+        <v>-0.011866582094926473</v>
       </c>
       <c r="H1" s="0">
-        <v>-0.057942872760641577</v>
+        <v>-0.056559023814314109</v>
       </c>
       <c r="I1" s="0">
-        <v>0.01104402971519374</v>
+        <v>0.047698508640042943</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.232886317181623</v>
+        <v>0.23034872416473601</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.098656248818357203</v>
+        <v>-0.10513365942243</v>
       </c>
       <c r="C2" s="0">
-        <v>0.34317058377056803</v>
+        <v>0.34712252425143297</v>
       </c>
       <c r="D2" s="0">
-        <v>0.24733824783409461</v>
+        <v>0.24414067239670553</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.059042708574460187</v>
+        <v>-0.072180052350297175</v>
       </c>
       <c r="F2" s="0">
-        <v>0.31823451991683366</v>
+        <v>0.26497040947843875</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.016435037884224606</v>
+        <v>-0.014048379445774521</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.040528253530128053</v>
+        <v>-0.034008159057678782</v>
       </c>
       <c r="I2" s="0">
-        <v>0.026999506916619228</v>
+        <v>0.082680804087698109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.26218843085335602</v>
+        <v>0.26385127861135799</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.0464047738771107</v>
+        <v>-0.049162017109316898</v>
       </c>
       <c r="C3" s="0">
-        <v>0.39669844705586499</v>
+        <v>0.40215512011849203</v>
       </c>
       <c r="D3" s="0">
-        <v>0.28096102733559503</v>
+        <v>0.27774412138913146</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.023477180383277528</v>
+        <v>-0.035307694119845738</v>
       </c>
       <c r="F3" s="0">
-        <v>0.34513188311962323</v>
+        <v>0.29337449562282109</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.016601590354330686</v>
+        <v>-0.014113537079854228</v>
       </c>
       <c r="H3" s="0">
-        <v>-0.022546734651766556</v>
+        <v>-0.010201424161564835</v>
       </c>
       <c r="I3" s="0">
-        <v>0.04867358068052044</v>
+        <v>0.10675774980230242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.299754753755406</v>
+        <v>0.29786731940736699</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0038496210259159401</v>
+        <v>0.020267376723266201</v>
       </c>
       <c r="C4" s="0">
-        <v>0.41700324504947101</v>
+        <v>0.42448056699930697</v>
       </c>
       <c r="D4" s="0">
-        <v>0.31501266383016391</v>
+        <v>0.31047383855160382</v>
       </c>
       <c r="E4" s="0">
-        <v>0.011083821222671947</v>
+        <v>0.0012917908348070331</v>
       </c>
       <c r="F4" s="0">
-        <v>0.37124907747821434</v>
+        <v>0.32138009717734839</v>
       </c>
       <c r="G4" s="0">
-        <v>-0.01611441743164203</v>
+        <v>-0.0095559960634767054</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.0077339528174707704</v>
+        <v>0.011059536458185016</v>
       </c>
       <c r="I4" s="0">
-        <v>0.046472511375740523</v>
+        <v>0.10216771098932602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.33402569579128999</v>
+        <v>0.33620861755255099</v>
       </c>
       <c r="B5" s="0">
-        <v>0.048392791221753502</v>
+        <v>0.041815473637286001</v>
       </c>
       <c r="C5" s="0">
-        <v>0.44170294793562898</v>
+        <v>0.42913979327794499</v>
       </c>
       <c r="D5" s="0">
-        <v>0.34869787155706722</v>
+        <v>0.34524771359543449</v>
       </c>
       <c r="E5" s="0">
-        <v>0.044488138722805846</v>
+        <v>0.033906624880976968</v>
       </c>
       <c r="F5" s="0">
-        <v>0.39744411823556253</v>
+        <v>0.34847139271343136</v>
       </c>
       <c r="G5" s="0">
-        <v>-0.015344942932796366</v>
+        <v>-0.011202516527247177</v>
       </c>
       <c r="H5" s="0">
-        <v>0.0015564143834042002</v>
+        <v>0.0096369121537379573</v>
       </c>
       <c r="I5" s="0">
-        <v>0.045926734395667301</v>
+        <v>0.084940542942711583</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.36044752058660701</v>
+        <v>0.35839847508406503</v>
       </c>
       <c r="B6" s="0">
-        <v>0.080371852557594506</v>
+        <v>0.073896771144341206</v>
       </c>
       <c r="C6" s="0">
-        <v>0.48581420281010601</v>
+        <v>0.485434735754947</v>
       </c>
       <c r="D6" s="0">
-        <v>0.38239527847350541</v>
+        <v>0.37870807920011379</v>
       </c>
       <c r="E6" s="0">
-        <v>0.076347656590785587</v>
+        <v>0.066362062232518268</v>
       </c>
       <c r="F6" s="0">
-        <v>0.42387148525222235</v>
+        <v>0.37672806069914649</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.013682549875663429</v>
+        <v>-0.011602702094934492</v>
       </c>
       <c r="H6" s="0">
-        <v>0.0059883078225043346</v>
+        <v>0.011008773400670826</v>
       </c>
       <c r="I6" s="0">
-        <v>0.060916109787698867</v>
+        <v>0.10653700384032026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.41716297753982301</v>
+        <v>0.41874846618726402</v>
       </c>
       <c r="B7" s="0">
-        <v>0.123242604680055</v>
+        <v>0.12347344192192</v>
       </c>
       <c r="C7" s="0">
-        <v>0.52792995599239401</v>
+        <v>0.533019213669641</v>
       </c>
       <c r="D7" s="0">
-        <v>0.41725498737208894</v>
+        <v>0.41334800902119251</v>
       </c>
       <c r="E7" s="0">
-        <v>0.10759118438053709</v>
+        <v>0.098920548177476045</v>
       </c>
       <c r="F7" s="0">
-        <v>0.44991106554559956</v>
+        <v>0.40448431086941472</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.0026840901191903712</v>
+        <v>0.00083148564030987031</v>
       </c>
       <c r="H7" s="0">
-        <v>0.014451692570593005</v>
+        <v>0.023713944230427719</v>
       </c>
       <c r="I7" s="0">
-        <v>0.077749770568413923</v>
+        <v>0.12828123464157651</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.45844238755400502</v>
+        <v>0.45734870530444699</v>
       </c>
       <c r="B8" s="0">
-        <v>0.16017855638906001</v>
+        <v>0.169692817500186</v>
       </c>
       <c r="C8" s="0">
-        <v>0.56698441771276398</v>
+        <v>0.57257772614958602</v>
       </c>
       <c r="D8" s="0">
-        <v>0.45171169093570301</v>
+        <v>0.44711957501170474</v>
       </c>
       <c r="E8" s="0">
-        <v>0.13820914524882502</v>
+        <v>0.13095217630536052</v>
       </c>
       <c r="F8" s="0">
-        <v>0.47578573489227888</v>
+        <v>0.43210108098331318</v>
       </c>
       <c r="G8" s="0">
-        <v>0.007599978719651102</v>
+        <v>0.013546384098749552</v>
       </c>
       <c r="H8" s="0">
-        <v>0.021442639005739752</v>
+        <v>0.033927215305538633</v>
       </c>
       <c r="I8" s="0">
-        <v>0.092125277402067426</v>
+        <v>0.13992636665044525</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.50379797465111298</v>
+        <v>0.50477841163818304</v>
       </c>
       <c r="B9" s="0">
-        <v>0.195046692840042</v>
+        <v>0.19027303383254501</v>
       </c>
       <c r="C9" s="0">
-        <v>0.61205597258352196</v>
+        <v>0.60023807713242605</v>
       </c>
       <c r="D9" s="0">
-        <v>0.48614444449183253</v>
+        <v>0.48235405242380791</v>
       </c>
       <c r="E9" s="0">
-        <v>0.16858517905440709</v>
+        <v>0.16103663907352397</v>
       </c>
       <c r="F9" s="0">
-        <v>0.50162103874686492</v>
+        <v>0.45897398146753615</v>
       </c>
       <c r="G9" s="0">
-        <v>0.017660079101956137</v>
+        <v>0.021516814907233166</v>
       </c>
       <c r="H9" s="0">
-        <v>0.032621153068493856</v>
+        <v>0.037959581577299853</v>
       </c>
       <c r="I9" s="0">
-        <v>0.10862532248045985</v>
+        <v>0.14213771529853458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.55411535214324703</v>
+        <v>0.55264621547668502</v>
       </c>
       <c r="B10" s="0">
-        <v>0.26216525174025701</v>
+        <v>0.25827593079720901</v>
       </c>
       <c r="C10" s="0">
-        <v>0.63986439682222496</v>
+        <v>0.64141637180399302</v>
       </c>
       <c r="D10" s="0">
-        <v>0.51911575854975134</v>
+        <v>0.51521013313447472</v>
       </c>
       <c r="E10" s="0">
-        <v>0.20033738299093881</v>
+        <v>0.1934153936164193</v>
       </c>
       <c r="F10" s="0">
-        <v>0.52720447697767192</v>
+        <v>0.48641392225763924</v>
       </c>
       <c r="G10" s="0">
-        <v>0.031895687365932228</v>
+        <v>0.03481939658890959</v>
       </c>
       <c r="H10" s="0">
-        <v>0.054090286835179371</v>
+        <v>0.058201908165204097</v>
       </c>
       <c r="I10" s="0">
-        <v>0.11322365962202288</v>
+        <v>0.15414084022794447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.58616838773733504</v>
+        <v>0.58759732458279301</v>
       </c>
       <c r="B11" s="0">
-        <v>0.28869610613529301</v>
+        <v>0.29046965486757398</v>
       </c>
       <c r="C11" s="0">
-        <v>0.665249844896589</v>
+        <v>0.66956147655611797</v>
       </c>
       <c r="D11" s="0">
-        <v>0.55251486980191011</v>
+        <v>0.54858299346720918</v>
       </c>
       <c r="E11" s="0">
-        <v>0.2294618181607268</v>
+        <v>0.22353953654820022</v>
       </c>
       <c r="F11" s="0">
-        <v>0.55220552163551972</v>
+        <v>0.51304042866769928</v>
       </c>
       <c r="G11" s="0">
-        <v>0.036528339607064808</v>
+        <v>0.040709952761979008</v>
       </c>
       <c r="H11" s="0">
-        <v>0.062568606515490607</v>
+        <v>0.06958167300998519</v>
       </c>
       <c r="I11" s="0">
-        <v>0.11420523615685393</v>
+        <v>0.15787289057611442</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.62732967235416204</v>
+        <v>0.62690332116139103</v>
       </c>
       <c r="B12" s="0">
-        <v>0.33663108801864799</v>
+        <v>0.340760971460633</v>
       </c>
       <c r="C12" s="0">
-        <v>0.70730451009539197</v>
+        <v>0.71145041655287</v>
       </c>
       <c r="D12" s="0">
-        <v>0.58509637753937904</v>
+        <v>0.581021385903146</v>
       </c>
       <c r="E12" s="0">
-        <v>0.25883916690871861</v>
+        <v>0.25367746409058056</v>
       </c>
       <c r="F12" s="0">
-        <v>0.57730013605889841</v>
+        <v>0.53973151550352172</v>
       </c>
       <c r="G12" s="0">
-        <v>0.043271760821740245</v>
+        <v>0.048137018391142518</v>
       </c>
       <c r="H12" s="0">
-        <v>0.078475056016852063</v>
+        <v>0.086098635069037893</v>
       </c>
       <c r="I12" s="0">
-        <v>0.1301546560311215</v>
+        <v>0.1710434318213146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.67779544726635299</v>
+        <v>0.67790048769782596</v>
       </c>
       <c r="B13" s="0">
-        <v>0.386096116561158</v>
+        <v>0.38323885338108898</v>
       </c>
       <c r="C13" s="0">
-        <v>0.74929023344865697</v>
+        <v>0.74315635716149098</v>
       </c>
       <c r="D13" s="0">
-        <v>0.61708573724930138</v>
+        <v>0.61351953927936986</v>
       </c>
       <c r="E13" s="0">
-        <v>0.28795146480220796</v>
+        <v>0.28280133533718205</v>
       </c>
       <c r="F13" s="0">
-        <v>0.60204647504597586</v>
+        <v>0.56571411044432851</v>
       </c>
       <c r="G13" s="0">
-        <v>0.053186309223917504</v>
+        <v>0.056402347182389477</v>
       </c>
       <c r="H13" s="0">
-        <v>0.09885806371892196</v>
+        <v>0.1025494243132835</v>
       </c>
       <c r="I13" s="0">
-        <v>0.14553926703034434</v>
+        <v>0.17693523332784972</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.70165446410029997</v>
+        <v>0.70053425007842396</v>
       </c>
       <c r="B14" s="0">
-        <v>0.43347544617966499</v>
+        <v>0.43159540564891602</v>
       </c>
       <c r="C14" s="0">
-        <v>0.76625022615562199</v>
+        <v>0.76468422328394403</v>
       </c>
       <c r="D14" s="0">
-        <v>0.64679016885510365</v>
+        <v>0.64327565702989387</v>
       </c>
       <c r="E14" s="0">
-        <v>0.3167379126764272</v>
+        <v>0.31209384125562317</v>
       </c>
       <c r="F14" s="0">
-        <v>0.62617260277372522</v>
+        <v>0.59145751427412174</v>
       </c>
       <c r="G14" s="0">
-        <v>0.060419510996241869</v>
+        <v>0.063156449121556532</v>
       </c>
       <c r="H14" s="0">
-        <v>0.11541844398438419</v>
+        <v>0.11873557626742079</v>
       </c>
       <c r="I14" s="0">
-        <v>0.14045205142027398</v>
+        <v>0.17338570848484455</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.74788792010609295</v>
+        <v>0.74916827329986602</v>
       </c>
       <c r="B15" s="0">
-        <v>0.469006886291787</v>
+        <v>0.47108416191451502</v>
       </c>
       <c r="C15" s="0">
-        <v>0.79553205442262998</v>
+        <v>0.79856967775572896</v>
       </c>
       <c r="D15" s="0">
-        <v>0.67685321785640884</v>
+        <v>0.67340072025001774</v>
       </c>
       <c r="E15" s="0">
-        <v>0.34363151343844189</v>
+        <v>0.33966501551037381</v>
       </c>
       <c r="F15" s="0">
-        <v>0.64956910808915513</v>
+        <v>0.61645476029556623</v>
       </c>
       <c r="G15" s="0">
-        <v>0.069709596475926353</v>
+        <v>0.073684707731061741</v>
       </c>
       <c r="H15" s="0">
-        <v>0.12275355521985334</v>
+        <v>0.12792422967845132</v>
       </c>
       <c r="I15" s="0">
-        <v>0.1325268309124672</v>
+        <v>0.16857273729373534</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.77853048182134299</v>
+        <v>0.778472915352863</v>
       </c>
       <c r="B16" s="0">
-        <v>0.48546257128249098</v>
+        <v>0.48678196137650298</v>
       </c>
       <c r="C16" s="0">
-        <v>0.80490519195402399</v>
+        <v>0.80847990315871399</v>
       </c>
       <c r="D16" s="0">
-        <v>0.7061397666488145</v>
+        <v>0.70277766049393198</v>
       </c>
       <c r="E16" s="0">
-        <v>0.36872781371181196</v>
+        <v>0.36512294074268986</v>
       </c>
       <c r="F16" s="0">
-        <v>0.65506182596140472</v>
+        <v>0.62343593597112335</v>
       </c>
       <c r="G16" s="0">
-        <v>0.072082503421933064</v>
+        <v>0.07593686444699134</v>
       </c>
       <c r="H16" s="0">
-        <v>0.11820157361298642</v>
+        <v>0.12281751965231584</v>
       </c>
       <c r="I16" s="0">
-        <v>0.13342599680488801</v>
+        <v>0.16778989757306101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.804068958724102</v>
+        <v>0.80381871046684905</v>
       </c>
       <c r="B17" s="0">
-        <v>0.50635254618450698</v>
+        <v>0.50464106245093698</v>
       </c>
       <c r="C17" s="0">
-        <v>0.82225868565211602</v>
+        <v>0.81729782288422803</v>
       </c>
       <c r="D17" s="0">
-        <v>0.73403340336837553</v>
+        <v>0.73100493787765364</v>
       </c>
       <c r="E17" s="0">
-        <v>0.39366601894253794</v>
+        <v>0.39017232554799025</v>
       </c>
       <c r="F17" s="0">
-        <v>0.67779026559643807</v>
+        <v>0.64739175519299719</v>
       </c>
       <c r="G17" s="0">
-        <v>0.069797335698401686</v>
+        <v>0.072299258139694261</v>
       </c>
       <c r="H17" s="0">
-        <v>0.11465418019166926</v>
+        <v>0.11709111817267664</v>
       </c>
       <c r="I17" s="0">
-        <v>0.14214203655365221</v>
+        <v>0.16868062687810181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.82836161602080705</v>
+        <v>0.827379694483243</v>
       </c>
       <c r="B18" s="0">
-        <v>0.534670589878394</v>
+        <v>0.53391786519832096</v>
       </c>
       <c r="C18" s="0">
-        <v>0.83117159222404402</v>
+        <v>0.830127490794629</v>
       </c>
       <c r="D18" s="0">
-        <v>0.76077967143339376</v>
+        <v>0.75781064040869439</v>
       </c>
       <c r="E18" s="0">
-        <v>0.4187423361609488</v>
+        <v>0.41562753102176847</v>
       </c>
       <c r="F18" s="0">
-        <v>0.69950338261851452</v>
+        <v>0.67061957797236416</v>
       </c>
       <c r="G18" s="0">
-        <v>0.065644855608438218</v>
+        <v>0.068132963015027331</v>
       </c>
       <c r="H18" s="0">
-        <v>0.11463509588524609</v>
+        <v>0.11719071271430984</v>
       </c>
       <c r="I18" s="0">
-        <v>0.13186753575354124</v>
+        <v>0.1594709077648275</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.84707504333436301</v>
+        <v>0.84835086481104505</v>
       </c>
       <c r="B19" s="0">
-        <v>0.55565458623846398</v>
+        <v>0.55697233628172305</v>
       </c>
       <c r="C19" s="0">
-        <v>0.83573903477000899</v>
+        <v>0.83771551510034903</v>
       </c>
       <c r="D19" s="0">
-        <v>0.78644090015410162</v>
+        <v>0.7836248823649532</v>
       </c>
       <c r="E19" s="0">
-        <v>0.44321477388019914</v>
+        <v>0.44048359234717399</v>
       </c>
       <c r="F19" s="0">
-        <v>0.72059289405710225</v>
+        <v>0.69315873658569349</v>
       </c>
       <c r="G19" s="0">
-        <v>0.059884660794924618</v>
+        <v>0.063429859001863237</v>
       </c>
       <c r="H19" s="0">
-        <v>0.11369402754043706</v>
+        <v>0.11710460040351522</v>
       </c>
       <c r="I19" s="0">
-        <v>0.11686019007513083</v>
+        <v>0.14635221149508484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.86851145666905205</v>
+        <v>0.86853860467489397</v>
       </c>
       <c r="B20" s="0">
-        <v>0.583232622339246</v>
+        <v>0.58343858989609199</v>
       </c>
       <c r="C20" s="0">
-        <v>0.85584344397685197</v>
+        <v>0.85914274404847102</v>
       </c>
       <c r="D20" s="0">
-        <v>0.81053743242417475</v>
+        <v>0.80787135846825675</v>
       </c>
       <c r="E20" s="0">
-        <v>0.46767786203402356</v>
+        <v>0.4650985072031798</v>
       </c>
       <c r="F20" s="0">
-        <v>0.74154324907518965</v>
+        <v>0.71549093306391309</v>
       </c>
       <c r="G20" s="0">
-        <v>0.05681432989870111</v>
+        <v>0.059873295081648098</v>
       </c>
       <c r="H20" s="0">
-        <v>0.11545868142971462</v>
+        <v>0.11777165494420755</v>
       </c>
       <c r="I20" s="0">
-        <v>0.11232432642809133</v>
+        <v>0.14054781376030384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.88617890660978904</v>
+        <v>0.88576831446323501</v>
       </c>
       <c r="B21" s="0">
-        <v>0.60797977728093799</v>
+        <v>0.60363100537955805</v>
       </c>
       <c r="C21" s="0">
-        <v>0.85741581256950195</v>
+        <v>0.85105416081762497</v>
       </c>
       <c r="D21" s="0">
-        <v>0.83359444391170345</v>
+        <v>0.8313636234419346</v>
       </c>
       <c r="E21" s="0">
-        <v>0.49138499569876382</v>
+        <v>0.48876469908585718</v>
       </c>
       <c r="F21" s="0">
-        <v>0.76147427368792397</v>
+        <v>0.73648091183344533</v>
       </c>
       <c r="G21" s="0">
-        <v>0.053301284847867454</v>
+        <v>0.054461520417567105</v>
       </c>
       <c r="H21" s="0">
-        <v>0.11322695011070659</v>
+        <v>0.11361802901152934</v>
       </c>
       <c r="I21" s="0">
-        <v>0.097811007014818707</v>
+        <v>0.118038300839233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.90241457649765799</v>
+        <v>0.90158683143204899</v>
       </c>
       <c r="B22" s="0">
-        <v>0.61561888604761394</v>
+        <v>0.61913064457803202</v>
       </c>
       <c r="C22" s="0">
-        <v>0.87478744760976102</v>
+        <v>0.87647748440273199</v>
       </c>
       <c r="D22" s="0">
-        <v>0.85632319606954133</v>
+        <v>0.8538186185930482</v>
       </c>
       <c r="E22" s="0">
-        <v>0.51360212918914305</v>
+        <v>0.51169318259517427</v>
       </c>
       <c r="F22" s="0">
-        <v>0.78095849195134748</v>
+        <v>0.75751875795859314</v>
       </c>
       <c r="G22" s="0">
-        <v>0.047828452652438028</v>
+        <v>0.050252808393858553</v>
       </c>
       <c r="H22" s="0">
-        <v>0.10512996326208585</v>
+        <v>0.10853308854797714</v>
       </c>
       <c r="I22" s="0">
-        <v>0.093010119204836997</v>
+        <v>0.11725920591015095</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.92693953330173195</v>
+        <v>0.92810849978448795</v>
       </c>
       <c r="B23" s="0">
-        <v>0.63908642755561795</v>
+        <v>0.63949922037890705</v>
       </c>
       <c r="C23" s="0">
-        <v>0.887777142744265</v>
+        <v>0.88859165537036799</v>
       </c>
       <c r="D23" s="0">
-        <v>0.87793719811911897</v>
+        <v>0.87580050756356209</v>
       </c>
       <c r="E23" s="0">
-        <v>0.53634739843753176</v>
+        <v>0.53443022341955027</v>
       </c>
       <c r="F23" s="0">
-        <v>0.79983261861158239</v>
+        <v>0.77757610550970835</v>
       </c>
       <c r="G23" s="0">
-        <v>0.045728097476774934</v>
+        <v>0.048504402690456173</v>
       </c>
       <c r="H23" s="0">
-        <v>0.10364765869044471</v>
+        <v>0.1064299422853402</v>
       </c>
       <c r="I23" s="0">
-        <v>0.087749296043297426</v>
+        <v>0.111312947502638</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.94362439785109598</v>
+        <v>0.94369543774823295</v>
       </c>
       <c r="B24" s="0">
-        <v>0.66491808645777295</v>
+        <v>0.66465944834409996</v>
       </c>
       <c r="C24" s="0">
-        <v>0.89642947469327805</v>
+        <v>0.89968011128637204</v>
       </c>
       <c r="D24" s="0">
-        <v>0.8978660121511427</v>
+        <v>0.89582512628539934</v>
       </c>
       <c r="E24" s="0">
-        <v>0.55934302106574596</v>
+        <v>0.55750973182471586</v>
       </c>
       <c r="F24" s="0">
-        <v>0.81821931799893666</v>
+        <v>0.79723946629304043</v>
       </c>
       <c r="G24" s="0">
-        <v>0.044659958787173756</v>
+        <v>0.046871669910335131</v>
       </c>
       <c r="H24" s="0">
-        <v>0.10473681059876043</v>
+        <v>0.10671101262534656</v>
       </c>
       <c r="I24" s="0">
-        <v>0.077917759895105146</v>
+        <v>0.1013002755757211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.95832527611253804</v>
+        <v>0.95792494658550498</v>
       </c>
       <c r="B25" s="0">
-        <v>0.68488795181432705</v>
+        <v>0.68504137118673303</v>
       </c>
       <c r="C25" s="0">
-        <v>0.89913474563308105</v>
+        <v>0.89656724988247705</v>
       </c>
       <c r="D25" s="0">
-        <v>0.91686423028730979</v>
+        <v>0.91493780009571257</v>
       </c>
       <c r="E25" s="0">
-        <v>0.58161961836231379</v>
+        <v>0.5799406750777748</v>
       </c>
       <c r="F25" s="0">
-        <v>0.83593356538569019</v>
+        <v>0.81602949069458686</v>
       </c>
       <c r="G25" s="0">
-        <v>0.042733165065417272</v>
+        <v>0.044265964511345769</v>
       </c>
       <c r="H25" s="0">
-        <v>0.10212687589910263</v>
+        <v>0.10374172019050343</v>
       </c>
       <c r="I25" s="0">
-        <v>0.063983307261793396</v>
+        <v>0.082096915031199397</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.97608438361535599</v>
+        <v>0.97527512609380296</v>
       </c>
       <c r="B26" s="0">
-        <v>0.69754031331273902</v>
+        <v>0.697622542074675</v>
       </c>
       <c r="C26" s="0">
-        <v>0.90902019391894495</v>
+        <v>0.90829704515950405</v>
       </c>
       <c r="D26" s="0">
-        <v>0.93538527828536555</v>
+        <v>0.93354612153368743</v>
       </c>
       <c r="E26" s="0">
-        <v>0.60288878060756657</v>
+        <v>0.60133804623830989</v>
       </c>
       <c r="F26" s="0">
-        <v>0.85316661718617737</v>
+        <v>0.83446619748483963</v>
       </c>
       <c r="G26" s="0">
-        <v>0.039676678433728511</v>
+        <v>0.04128719719855535</v>
       </c>
       <c r="H26" s="0">
-        <v>0.09515046158544542</v>
+        <v>0.096699541342934681</v>
       </c>
       <c r="I26" s="0">
-        <v>0.055792019565622637</v>
+        <v>0.073493870940578396</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.98546578061532997</v>
+        <v>0.98650699696856503</v>
       </c>
       <c r="B27" s="0">
-        <v>0.71132172998004695</v>
+        <v>0.71114857043903301</v>
       </c>
       <c r="C27" s="0">
-        <v>0.92012840801707596</v>
+        <v>0.91977185451350896</v>
       </c>
       <c r="D27" s="0">
-        <v>0.95280691699399755</v>
+        <v>0.95121211603760003</v>
       </c>
       <c r="E27" s="0">
-        <v>0.62381628728983074</v>
+        <v>0.62230968148321364</v>
       </c>
       <c r="F27" s="0">
-        <v>0.86995381423096463</v>
+        <v>0.85235321366582129</v>
       </c>
       <c r="G27" s="0">
-        <v>0.034897273055283576</v>
+        <v>0.036813356232366555</v>
       </c>
       <c r="H27" s="0">
-        <v>0.087231387773760202</v>
+        <v>0.088579092522518582</v>
       </c>
       <c r="I27" s="0">
-        <v>0.049705760216275388</v>
+        <v>0.067302943873401258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>1.00149134972281</v>
+        <v>1.00175821906179</v>
       </c>
       <c r="B28" s="0">
-        <v>0.72431440242374001</v>
+        <v>0.72380786049684398</v>
       </c>
       <c r="C28" s="0">
-        <v>0.92733820908195597</v>
+        <v>0.93013274115228395</v>
       </c>
       <c r="D28" s="0">
-        <v>0.97005238574666697</v>
+        <v>0.96851730613770726</v>
       </c>
       <c r="E28" s="0">
-        <v>0.64417752584017818</v>
+        <v>0.6427796105714052</v>
       </c>
       <c r="F28" s="0">
-        <v>0.88607979596999042</v>
+        <v>0.86963483296759314</v>
       </c>
       <c r="G28" s="0">
-        <v>0.030192602574666837</v>
+        <v>0.031811304585546318</v>
       </c>
       <c r="H28" s="0">
-        <v>0.079607751721573236</v>
+        <v>0.080938395725873122</v>
       </c>
       <c r="I28" s="0">
-        <v>0.041984591852447975</v>
+        <v>0.060316772179179766</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>1.01195812225805</v>
+        <v>1.0113721758410601</v>
       </c>
       <c r="B29" s="0">
-        <v>0.73447829537532605</v>
+        <v>0.73539796886228304</v>
       </c>
       <c r="C29" s="0">
-        <v>0.94064147740926696</v>
+        <v>0.93789433781645304</v>
       </c>
       <c r="D29" s="0">
-        <v>0.98646749451447713</v>
+        <v>0.98494607479674534</v>
       </c>
       <c r="E29" s="0">
-        <v>0.6484819449494641</v>
+        <v>0.64727160382950111</v>
       </c>
       <c r="F29" s="0">
-        <v>0.90192535505462723</v>
+        <v>0.88643429924853534</v>
       </c>
       <c r="G29" s="0">
-        <v>0.02526677556082528</v>
+        <v>0.026488278203742395</v>
       </c>
       <c r="H29" s="0">
-        <v>0.074487288154274287</v>
+        <v>0.076040899156210845</v>
       </c>
       <c r="I29" s="0">
-        <v>0.036986064565308459</v>
+        <v>0.05085241843113969</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>1.02783911433288</v>
+        <v>1.0272536023873799</v>
       </c>
       <c r="B30" s="0">
-        <v>0.75049057488013005</v>
+        <v>0.75047801562365901</v>
       </c>
       <c r="C30" s="0">
-        <v>0.94094463457307298</v>
+        <v>0.94257607140323096</v>
       </c>
       <c r="D30" s="0">
-        <v>1.0014797602741463</v>
+        <v>1.0000296363848571</v>
       </c>
       <c r="E30" s="0">
-        <v>0.66957119375213348</v>
+        <v>0.66839313066007522</v>
       </c>
       <c r="F30" s="0">
-        <v>0.91728630201607209</v>
+        <v>0.90291096299796403</v>
       </c>
       <c r="G30" s="0">
-        <v>0.024965022012787719</v>
+        <v>0.026406422271238083</v>
       </c>
       <c r="H30" s="0">
-        <v>0.076316000363566935</v>
+        <v>0.077646429658377106</v>
       </c>
       <c r="I30" s="0">
-        <v>0.026094355666584353</v>
+        <v>0.041144780319023903</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.0368415987864901</v>
+        <v>1.0376215554222501</v>
       </c>
       <c r="B31" s="0">
-        <v>0.75757173931875399</v>
+        <v>0.75705034716028496</v>
       </c>
       <c r="C31" s="0">
-        <v>0.95890076570203797</v>
+        <v>0.95676910401260495</v>
       </c>
       <c r="D31" s="0">
-        <v>1.0162865146349402</v>
+        <v>1.01507533981623</v>
       </c>
       <c r="E31" s="0">
-        <v>0.68890487693444458</v>
+        <v>0.68770003613484787</v>
       </c>
       <c r="F31" s="0">
-        <v>0.93252138127651207</v>
+        <v>0.91902090009126258</v>
       </c>
       <c r="G31" s="0">
-        <v>0.021204861985501377</v>
+        <v>0.022762122643525003</v>
       </c>
       <c r="H31" s="0">
-        <v>0.06933838977447776</v>
+        <v>0.070009220193681637</v>
       </c>
       <c r="I31" s="0">
-        <v>0.02519869321446631</v>
+        <v>0.037430736547467036</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>1.0440211686665699</v>
+        <v>1.04445076473676</v>
       </c>
       <c r="B32" s="0">
-        <v>0.76626484086761903</v>
+        <v>0.76561247716353797</v>
       </c>
       <c r="C32" s="0">
-        <v>0.96342953767239203</v>
+        <v>0.96538938358182003</v>
       </c>
       <c r="D32" s="0">
-        <v>1.0305812900850371</v>
+        <v>1.0294384419928817</v>
       </c>
       <c r="E32" s="0">
-        <v>0.70760312656176672</v>
+        <v>0.70644511972070823</v>
       </c>
       <c r="F32" s="0">
-        <v>0.94713186366337321</v>
+        <v>0.93466635349048954</v>
       </c>
       <c r="G32" s="0">
-        <v>0.014247175797689107</v>
+        <v>0.015546607710884636</v>
       </c>
       <c r="H32" s="0">
-        <v>0.059590662473161082</v>
+        <v>0.059930216619035276</v>
       </c>
       <c r="I32" s="0">
-        <v>0.015810925739516715</v>
+        <v>0.029228534609965492</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>1.0524569044149901</v>
+        <v>1.0518522433564701</v>
       </c>
       <c r="B33" s="0">
-        <v>0.777085695540782</v>
+        <v>0.77489739144743297</v>
       </c>
       <c r="C33" s="0">
-        <v>0.96049511999317705</v>
+        <v>0.95754082785598504</v>
       </c>
       <c r="D33" s="0">
-        <v>1.0443841561236187</v>
+        <v>1.0433988118414232</v>
       </c>
       <c r="E33" s="0">
-        <v>0.72599937764451794</v>
+        <v>0.72486288581320679</v>
       </c>
       <c r="F33" s="0">
-        <v>0.96130972129845615</v>
+        <v>0.94963525459041687</v>
       </c>
       <c r="G33" s="0">
-        <v>0.0080305055948448698</v>
+        <v>0.008280232612000343</v>
       </c>
       <c r="H33" s="0">
-        <v>0.050534469000838522</v>
+        <v>0.050636751286268662</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.00057964367070288767</v>
+        <v>0.0094533178538051075</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>1.06107673537104</v>
+        <v>1.06050417832581</v>
       </c>
       <c r="B34" s="0">
-        <v>0.78372897185146695</v>
+        <v>0.787134626290932</v>
       </c>
       <c r="C34" s="0">
-        <v>0.95948814870750498</v>
+        <v>0.96397810546922602</v>
       </c>
       <c r="D34" s="0">
-        <v>1.0578406899364794</v>
+        <v>1.0566140091032399</v>
       </c>
       <c r="E34" s="0">
-        <v>0.74379213020235513</v>
+        <v>0.74308018215043681</v>
       </c>
       <c r="F34" s="0">
-        <v>0.97522150891474302</v>
+        <v>0.96466333593823073</v>
       </c>
       <c r="G34" s="0">
-        <v>0.0033906382760512345</v>
+        <v>0.0047895253459223752</v>
       </c>
       <c r="H34" s="0">
-        <v>0.040612699487875867</v>
+        <v>0.043118156479154776</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.015539340609423122</v>
+        <v>-0.0020749035754084526</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>1.07260169064198</v>
+        <v>1.07330410620738</v>
       </c>
       <c r="B35" s="0">
-        <v>0.79317827705269695</v>
+        <v>0.792690515791031</v>
       </c>
       <c r="C35" s="0">
-        <v>0.96512889230300003</v>
+        <v>0.96111978862079706</v>
       </c>
       <c r="D35" s="0">
-        <v>1.0707828377473301</v>
+        <v>1.0699341262231561</v>
       </c>
       <c r="E35" s="0">
-        <v>0.76125750231726952</v>
+        <v>0.76033237012688604</v>
       </c>
       <c r="F35" s="0">
-        <v>0.98899615826091003</v>
+        <v>0.97904764392511889</v>
       </c>
       <c r="G35" s="0">
-        <v>0.0012857970252949334</v>
+        <v>0.0024035464244290573</v>
       </c>
       <c r="H35" s="0">
-        <v>0.030913193833642681</v>
+        <v>0.031935598045217096</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.023680642742563127</v>
+        <v>-0.016361157278788872</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>1.0804360459297</v>
+        <v>1.0809203013276301</v>
       </c>
       <c r="B36" s="0">
-        <v>0.79679592658466003</v>
+        <v>0.79596459231362404</v>
       </c>
       <c r="C36" s="0">
-        <v>0.97657515624084701</v>
+        <v>0.97782287290922199</v>
       </c>
       <c r="D36" s="0">
-        <v>1.0834762424046012</v>
+        <v>1.0826557397880099</v>
       </c>
       <c r="E36" s="0">
-        <v>0.77794843942295522</v>
+        <v>0.77704255756699381</v>
       </c>
       <c r="F36" s="0">
-        <v>1.0025794683459162</v>
+        <v>0.99356234910289154</v>
       </c>
       <c r="G36" s="0">
-        <v>-0.00094736160099022934</v>
+        <v>-5.9804285771765435e-05</v>
       </c>
       <c r="H36" s="0">
-        <v>0.018596639114710597</v>
+        <v>0.019256815693373178</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.025089439391549548</v>
+        <v>-0.015497146949605998</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>1.09323525567388</v>
+        <v>1.0925220894949299</v>
       </c>
       <c r="B37" s="0">
-        <v>0.79997261408051801</v>
+        <v>0.80148793446295197</v>
       </c>
       <c r="C37" s="0">
-        <v>0.99728643526952399</v>
+        <v>0.99834945377080597</v>
       </c>
       <c r="D37" s="0">
-        <v>1.0962583996767499</v>
+        <v>1.0953339523125074</v>
       </c>
       <c r="E37" s="0">
-        <v>0.79409734763566708</v>
+        <v>0.79338632367335027</v>
       </c>
       <c r="F37" s="0">
-        <v>1.0160743568827735</v>
+        <v>1.0078753190182879</v>
       </c>
       <c r="G37" s="0">
-        <v>-0.0028415440691865546</v>
+        <v>-0.0020292037971245914</v>
       </c>
       <c r="H37" s="0">
-        <v>0.0062895026031006699</v>
+        <v>0.0076561766707315291</v>
       </c>
       <c r="I37" s="0">
-        <v>-0.020960113720111809</v>
+        <v>-0.011214539377452053</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>1.1026428181724099</v>
+        <v>1.10236930410228</v>
       </c>
       <c r="B38" s="0">
-        <v>0.80496267587022197</v>
+        <v>0.80463350526609401</v>
       </c>
       <c r="C38" s="0">
-        <v>0.99625516279152304</v>
+        <v>0.99943280943192103</v>
       </c>
       <c r="D38" s="0">
-        <v>1.1089877273903963</v>
+        <v>1.1081980253306127</v>
       </c>
       <c r="E38" s="0">
-        <v>0.8100559224920949</v>
+        <v>0.80927525830583336</v>
       </c>
       <c r="F38" s="0">
-        <v>1.0289151583840794</v>
+        <v>1.0215116414541061</v>
       </c>
       <c r="G38" s="0">
-        <v>-0.0069785357348331892</v>
+        <v>-0.0062131054121911371</v>
       </c>
       <c r="H38" s="0">
-        <v>-0.0053205768055735363</v>
+        <v>-0.004381344124559902</v>
       </c>
       <c r="I38" s="0">
-        <v>-0.031511934151175099</v>
+        <v>-0.022178103143411985</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>1.1087649574821199</v>
+        <v>1.1091753208036099</v>
       </c>
       <c r="B39" s="0">
-        <v>0.81189298183172098</v>
+        <v>0.81163218469012299</v>
       </c>
       <c r="C39" s="0">
-        <v>1.00576374018327</v>
+        <v>0.999746060076804</v>
       </c>
       <c r="D39" s="0">
-        <v>1.121385224073373</v>
+        <v>1.1207959690177665</v>
       </c>
       <c r="E39" s="0">
-        <v>0.8260541988622897</v>
+        <v>0.82525669149192693</v>
       </c>
       <c r="F39" s="0">
-        <v>1.0418591441870897</v>
+        <v>1.034974206867306</v>
       </c>
       <c r="G39" s="0">
-        <v>-0.011687938333399612</v>
+        <v>-0.011158481172084065</v>
       </c>
       <c r="H39" s="0">
-        <v>-0.01301972304533794</v>
+        <v>-0.012735508702517769</v>
       </c>
       <c r="I39" s="0">
-        <v>-0.036235023652332853</v>
+        <v>-0.033800924767114784</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>1.12143377843153</v>
+        <v>1.1219047929549999</v>
       </c>
       <c r="B40" s="0">
-        <v>0.82844008349203402</v>
+        <v>0.82749014342418103</v>
       </c>
       <c r="C40" s="0">
-        <v>1.0184190941670399</v>
+        <v>1.0191387815309501</v>
       </c>
       <c r="D40" s="0">
-        <v>1.133641065299164</v>
+        <v>1.1330672767764289</v>
       </c>
       <c r="E40" s="0">
-        <v>0.84238928626219856</v>
+        <v>0.84164138727468951</v>
       </c>
       <c r="F40" s="0">
-        <v>1.0547295703181829</v>
+        <v>1.0486896893342148</v>
       </c>
       <c r="G40" s="0">
-        <v>-0.013565618179213649</v>
+        <v>-0.012960692277238612</v>
       </c>
       <c r="H40" s="0">
-        <v>-0.013680424105944899</v>
+        <v>-0.013292557095097366</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.036397711113959924</v>
+        <v>-0.03050743083768374</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>1.1310396710028201</v>
+        <v>1.13048624057531</v>
       </c>
       <c r="B41" s="0">
-        <v>0.85019629164875699</v>
+        <v>0.85170505735479096</v>
       </c>
       <c r="C41" s="0">
-        <v>1.0329102018479499</v>
+        <v>1.03357530574426</v>
       </c>
       <c r="D41" s="0">
-        <v>1.1454591861348167</v>
+        <v>1.144777012536258</v>
       </c>
       <c r="E41" s="0">
-        <v>0.85875678199084915</v>
+        <v>0.8581997543418135</v>
       </c>
       <c r="F41" s="0">
-        <v>1.0675534805597393</v>
+        <v>1.0622096467979671</v>
       </c>
       <c r="G41" s="0">
-        <v>-0.013885119169595716</v>
+        <v>-0.013235283409981731</v>
       </c>
       <c r="H41" s="0">
-        <v>-0.011002819297512307</v>
+        <v>-0.0098022689238184222</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.033817622544966168</v>
+        <v>-0.026988568116153907</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>1.1440151457494101</v>
+        <v>1.14379045860706</v>
       </c>
       <c r="B42" s="0">
-        <v>0.861331955435095</v>
+        <v>0.86093809120014297</v>
       </c>
       <c r="C42" s="0">
-        <v>1.05426890193111</v>
+        <v>1.0597688325140899</v>
       </c>
       <c r="D42" s="0">
-        <v>1.1576822047891373</v>
+        <v>1.1570787579249779</v>
       </c>
       <c r="E42" s="0">
-        <v>0.87426559520161129</v>
+        <v>0.87364383720724448</v>
       </c>
       <c r="F42" s="0">
-        <v>1.0802809355943677</v>
+        <v>1.0756808026804339</v>
       </c>
       <c r="G42" s="0">
-        <v>-0.014035052541885721</v>
+        <v>-0.013331241708055361</v>
       </c>
       <c r="H42" s="0">
-        <v>-0.0090430440902944768</v>
+        <v>-0.0081271975206350395</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.027683486207312862</v>
+        <v>-0.019469435729957883</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>1.15874132874604</v>
+        <v>1.1589865859124899</v>
       </c>
       <c r="B43" s="0">
-        <v>0.89298177137311496</v>
+        <v>0.89305403518066395</v>
       </c>
       <c r="C43" s="0">
-        <v>1.0637266559294301</v>
+        <v>1.0563781615124399</v>
       </c>
       <c r="D43" s="0">
-        <v>1.1690677355288035</v>
+        <v>1.1686410821286111</v>
       </c>
       <c r="E43" s="0">
-        <v>0.89053865788849584</v>
+        <v>0.88990926921328239</v>
       </c>
       <c r="F43" s="0">
-        <v>1.0928276164607744</v>
+        <v>1.0885629285721166</v>
       </c>
       <c r="G43" s="0">
-        <v>-0.0095619472615481264</v>
+        <v>-0.009080157482307661</v>
       </c>
       <c r="H43" s="0">
-        <v>-0.0012701737006278247</v>
+        <v>-0.001144852360934985</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.027939670029359542</v>
+        <v>-0.028904989262273723</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>1.1761475795774401</v>
+        <v>1.17658219728986</v>
       </c>
       <c r="B44" s="0">
-        <v>0.90484269910362203</v>
+        <v>0.90360189138594504</v>
       </c>
       <c r="C44" s="0">
-        <v>1.0840318835437099</v>
+        <v>1.0846455591037401</v>
       </c>
       <c r="D44" s="0">
-        <v>1.1811476859721111</v>
+        <v>1.1807783306520896</v>
       </c>
       <c r="E44" s="0">
-        <v>0.90540832892748557</v>
+        <v>0.90473890037666016</v>
       </c>
       <c r="F44" s="0">
-        <v>1.1053114958177575</v>
+        <v>1.1018002942679082</v>
       </c>
       <c r="G44" s="0">
-        <v>-0.0047764908905767152</v>
+        <v>-0.0042814950851764663</v>
       </c>
       <c r="H44" s="0">
-        <v>0.00075018268859892978</v>
+        <v>0.00030300143086192514</v>
       </c>
       <c r="I44" s="0">
-        <v>-0.020654770121622736</v>
+        <v>-0.017608459934914732</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>1.19276187863284</v>
+        <v>1.1923911942699399</v>
       </c>
       <c r="B45" s="0">
-        <v>0.92424534057382102</v>
+        <v>0.92225145092462602</v>
       </c>
       <c r="C45" s="0">
-        <v>1.1132811632956701</v>
+        <v>1.11361528586492</v>
       </c>
       <c r="D45" s="0">
-        <v>1.1928338769454077</v>
+        <v>1.1925573085284733</v>
       </c>
       <c r="E45" s="0">
-        <v>0.9202768391948114</v>
+        <v>0.91962480963481064</v>
       </c>
       <c r="F45" s="0">
-        <v>1.117969181099552</v>
+        <v>1.1149951986469657</v>
       </c>
       <c r="G45" s="0">
-        <v>0.00030842445851164625</v>
+        <v>9.1104825847658461e-05</v>
       </c>
       <c r="H45" s="0">
-        <v>0.0034399183183045491</v>
+        <v>0.0031192861656422727</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.0054760425847950617</v>
+        <v>-0.0013096712792425745</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>1.2076672394343</v>
+        <v>1.20744183060729</v>
       </c>
       <c r="B46" s="0">
-        <v>0.938895011958083</v>
+        <v>0.94193766982180804</v>
       </c>
       <c r="C46" s="0">
-        <v>1.1321805285965201</v>
+        <v>1.1386763600651799</v>
       </c>
       <c r="D46" s="0">
-        <v>1.2047192065156282</v>
+        <v>1.2042088645903575</v>
       </c>
       <c r="E46" s="0">
-        <v>0.93475587956304218</v>
+        <v>0.93448570251154894</v>
       </c>
       <c r="F46" s="0">
-        <v>1.1303279293174311</v>
+        <v>1.1280933756127032</v>
       </c>
       <c r="G46" s="0">
-        <v>0.0033979853812655214</v>
+        <v>0.0041076549423062231</v>
       </c>
       <c r="H46" s="0">
-        <v>0.0049053458940375135</v>
+        <v>0.0069993407542778023</v>
       </c>
       <c r="I46" s="0">
-        <v>0.0015202042653236624</v>
+        <v>0.0082903265062579806</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.2226997211803099</v>
+        <v>1.2227618696532001</v>
       </c>
       <c r="B47" s="0">
-        <v>0.95647430723752402</v>
+        <v>0.95680674616073802</v>
       </c>
       <c r="C47" s="0">
-        <v>1.1422471916313199</v>
+        <v>1.13472818959376</v>
       </c>
       <c r="D47" s="0">
-        <v>1.2165127887311618</v>
+        <v>1.2162785203739905</v>
       </c>
       <c r="E47" s="0">
-        <v>0.9492941789977698</v>
+        <v>0.94887618058373957</v>
       </c>
       <c r="F47" s="0">
-        <v>1.142552387964811</v>
+        <v>1.1405021788298582</v>
       </c>
       <c r="G47" s="0">
-        <v>0.0052809390127158545</v>
+        <v>0.0055421357206035683</v>
       </c>
       <c r="H47" s="0">
-        <v>0.0071259116319913355</v>
+        <v>0.007865363710925298</v>
       </c>
       <c r="I47" s="0">
-        <v>0.00051054068798008314</v>
+        <v>-0.002775771702219466</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>1.23279177526299</v>
+        <v>1.2332178782123699</v>
       </c>
       <c r="B48" s="0">
-        <v>0.97282688006693196</v>
+        <v>0.97144262441773699</v>
       </c>
       <c r="C48" s="0">
-        <v>1.1529520027853699</v>
+        <v>1.1533949649822699</v>
       </c>
       <c r="D48" s="0">
-        <v>1.2280035965987732</v>
+        <v>1.2278239333116636</v>
       </c>
       <c r="E48" s="0">
-        <v>0.96377438741374866</v>
+        <v>0.96328375642961472</v>
       </c>
       <c r="F48" s="0">
-        <v>1.1548775973684895</v>
+        <v>1.153479445567434</v>
       </c>
       <c r="G48" s="0">
-        <v>0.0049204563033691147</v>
+        <v>0.0051681987935847766</v>
       </c>
       <c r="H48" s="0">
-        <v>0.0087264569602320124</v>
+        <v>0.0087687735523698622</v>
       </c>
       <c r="I48" s="0">
-        <v>-0.003849835553288973</v>
+        <v>-0.0028680877181768553</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.2425541233058699</v>
+        <v>1.2424659049367399</v>
       </c>
       <c r="B49" s="0">
-        <v>0.98487165017469003</v>
+        <v>0.98642807114986397</v>
       </c>
       <c r="C49" s="0">
-        <v>1.14262456023226</v>
+        <v>1.14505191146661</v>
       </c>
       <c r="D49" s="0">
-        <v>1.2397262771139075</v>
+        <v>1.2394304097855311</v>
       </c>
       <c r="E49" s="0">
-        <v>0.97788362089134895</v>
+        <v>0.97758200956002461</v>
       </c>
       <c r="F49" s="0">
-        <v>1.1667019939262591</v>
+        <v>1.1658404741641923</v>
       </c>
       <c r="G49" s="0">
-        <v>0.001523218176955758</v>
+        <v>0.0019518844259656829</v>
       </c>
       <c r="H49" s="0">
-        <v>0.0078442519657058278</v>
+        <v>0.0087559777177151996</v>
       </c>
       <c r="I49" s="0">
-        <v>-0.021581899911218595</v>
+        <v>-0.018009985959432286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.24995526544962</v>
+        <v>1.2495726418141899</v>
       </c>
       <c r="B50" s="0">
-        <v>1.0008196247458001</v>
+        <v>1.0002676172599501</v>
       </c>
       <c r="C50" s="0">
-        <v>1.15644687673923</v>
+        <v>1.1605040721758799</v>
       </c>
       <c r="D50" s="0">
-        <v>1.2507324281456575</v>
+        <v>1.2505236676498428</v>
       </c>
       <c r="E50" s="0">
-        <v>0.99219455218133756</v>
+        <v>0.99182109845631639</v>
       </c>
       <c r="F50" s="0">
-        <v>1.1791443950555409</v>
+        <v>1.1787569806108227</v>
       </c>
       <c r="G50" s="0">
-        <v>-0.0013047103921596571</v>
+        <v>-0.0011959926536915784</v>
       </c>
       <c r="H50" s="0">
-        <v>0.0083171286693767763</v>
+        <v>0.008811183692306138</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.024425080511656917</v>
+        <v>-0.021290801500966329</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.2552293745010901</v>
+        <v>1.2551501178055</v>
       </c>
       <c r="B51" s="0">
-        <v>1.0124802299119899</v>
+        <v>1.0127823864288801</v>
       </c>
       <c r="C51" s="0">
-        <v>1.15655147171253</v>
+        <v>1.14980909846474</v>
       </c>
       <c r="D51" s="0">
-        <v>1.2618302839773385</v>
+        <v>1.2617480699624517</v>
       </c>
       <c r="E51" s="0">
-        <v>1.005982157655539</v>
+        <v>1.005635726591398</v>
       </c>
       <c r="F51" s="0">
-        <v>1.1912149250832496</v>
+        <v>1.1910239658506354</v>
       </c>
       <c r="G51" s="0">
-        <v>-0.0047294303072620333</v>
+        <v>-0.0048756272191058233</v>
       </c>
       <c r="H51" s="0">
-        <v>0.0052119035638807914</v>
+        <v>0.0052744554823439321</v>
       </c>
       <c r="I51" s="0">
-        <v>-0.033666218941145083</v>
+        <v>-0.038421706319695652</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.2656873231713599</v>
+        <v>1.2661692062214001</v>
       </c>
       <c r="B52" s="0">
-        <v>1.01689886099728</v>
+        <v>1.01566801549639</v>
       </c>
       <c r="C52" s="0">
-        <v>1.16765300112967</v>
+        <v>1.1681295201759001</v>
       </c>
       <c r="D52" s="0">
-        <v>1.273445535576371</v>
+        <v>1.2734170993165181</v>
       </c>
       <c r="E52" s="0">
-        <v>1.0189544672357713</v>
+        <v>1.0185966490639087</v>
       </c>
       <c r="F52" s="0">
-        <v>1.2033689312104106</v>
+        <v>1.203729950767819</v>
       </c>
       <c r="G52" s="0">
-        <v>-0.0075087967361426537</v>
+        <v>-0.0073630071070779146</v>
       </c>
       <c r="H52" s="0">
-        <v>-0.0022189014020110782</v>
+        <v>-0.0022451282992887065</v>
       </c>
       <c r="I52" s="0">
-        <v>-0.035370470905651437</v>
+        <v>-0.036240192044369728</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.27400736915698</v>
+        <v>1.27419383430037</v>
       </c>
       <c r="B53" s="0">
-        <v>1.0197501047233299</v>
+        <v>1.0214128231825299</v>
       </c>
       <c r="C53" s="0">
-        <v>1.18343143565967</v>
+        <v>1.1838665578566701</v>
       </c>
       <c r="D53" s="0">
-        <v>1.2851645697619019</v>
+        <v>1.285039498311966</v>
       </c>
       <c r="E53" s="0">
-        <v>1.0317404113944588</v>
+        <v>1.031570824144701</v>
       </c>
       <c r="F53" s="0">
-        <v>1.215602273165278</v>
+        <v>1.2163657851289131</v>
       </c>
       <c r="G53" s="0">
-        <v>-0.01048721809370644</v>
+        <v>-0.010107088598411527</v>
       </c>
       <c r="H53" s="0">
-        <v>-0.010722927034340165</v>
+        <v>-0.0099576392008284831</v>
       </c>
       <c r="I53" s="0">
-        <v>-0.033295701141027784</v>
+        <v>-0.032844409856075271</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.2842411928303099</v>
+        <v>1.2836393399338799</v>
       </c>
       <c r="B54" s="0">
-        <v>1.0283897802059501</v>
+        <v>1.0274844897212101</v>
       </c>
       <c r="C54" s="0">
-        <v>1.18824939762268</v>
+        <v>1.1932774222058899</v>
       </c>
       <c r="D54" s="0">
-        <v>1.2969682403485023</v>
+        <v>1.2968937159838041</v>
       </c>
       <c r="E54" s="0">
-        <v>1.0449161790813097</v>
+        <v>1.0446549910189802</v>
       </c>
       <c r="F54" s="0">
-        <v>1.2276578058022929</v>
+        <v>1.2288739199513812</v>
       </c>
       <c r="G54" s="0">
-        <v>-0.012480815034071167</v>
+        <v>-0.012547748105792579</v>
       </c>
       <c r="H54" s="0">
-        <v>-0.016974731254874569</v>
+        <v>-0.01677494280983045</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.038827281541779959</v>
+        <v>-0.036616549334406577</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.29579087197946</v>
+        <v>1.29557048678882</v>
       </c>
       <c r="B55" s="0">
-        <v>1.0351915074387901</v>
+        <v>1.03545442887398</v>
       </c>
       <c r="C55" s="0">
-        <v>1.1947485221960601</v>
+        <v>1.18941046652371</v>
       </c>
       <c r="D55" s="0">
-        <v>1.3089738171141718</v>
+        <v>1.3090182770306387</v>
       </c>
       <c r="E55" s="0">
-        <v>1.0581942379184996</v>
+        <v>1.0579697956454348</v>
       </c>
       <c r="F55" s="0">
-        <v>1.2398014012933229</v>
+        <v>1.2411366221114024</v>
       </c>
       <c r="G55" s="0">
-        <v>-0.014516973083288767</v>
+        <v>-0.014879063527139507</v>
       </c>
       <c r="H55" s="0">
-        <v>-0.022673781822309825</v>
+        <v>-0.022720705563902391</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.045200697752184736</v>
+        <v>-0.050273559841895729</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3037542384324301</v>
+        <v>1.3043196511098401</v>
       </c>
       <c r="B56" s="0">
-        <v>1.0434620309920499</v>
+        <v>1.0426006657911999</v>
       </c>
       <c r="C56" s="0">
-        <v>1.1965029348954099</v>
+        <v>1.1965487398485299</v>
       </c>
       <c r="D56" s="0">
-        <v>1.3207736731441859</v>
+        <v>1.3208833783638927</v>
       </c>
       <c r="E56" s="0">
-        <v>1.0718260107425297</v>
+        <v>1.0716049386345736</v>
       </c>
       <c r="F56" s="0">
-        <v>1.2519781616153505</v>
+        <v>1.2537464231056041</v>
       </c>
       <c r="G56" s="0">
-        <v>-0.018038868882341463</v>
+        <v>-0.017958754946978434</v>
       </c>
       <c r="H56" s="0">
-        <v>-0.027484200918551766</v>
+        <v>-0.02744558789770456</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.055814041077280371</v>
+        <v>-0.057937121885940586</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.3103414910514599</v>
+        <v>1.3108483884025499</v>
       </c>
       <c r="B57" s="0">
-        <v>1.0546188780200001</v>
+        <v>1.05640426438479</v>
       </c>
       <c r="C57" s="0">
-        <v>1.1934396633306401</v>
+        <v>1.19630301259842</v>
       </c>
       <c r="D57" s="0">
-        <v>1.3323181015137116</v>
+        <v>1.3323135629653666</v>
       </c>
       <c r="E57" s="0">
-        <v>1.085831802033665</v>
+        <v>1.0857853511518845</v>
       </c>
       <c r="F57" s="0">
-        <v>1.2641781139280943</v>
+        <v>1.2663409135288246</v>
       </c>
       <c r="G57" s="0">
-        <v>-0.021466581483855877</v>
+        <v>-0.02098567031931884</v>
       </c>
       <c r="H57" s="0">
-        <v>-0.031510291446445522</v>
+        <v>-0.030697598397428277</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.071118901081045655</v>
+        <v>-0.070604522034340186</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.3185500406281601</v>
+        <v>1.3177034888255501</v>
       </c>
       <c r="B58" s="0">
-        <v>1.0639473994184301</v>
+        <v>1.0626264638479901</v>
       </c>
       <c r="C58" s="0">
-        <v>1.1885737759261701</v>
+        <v>1.1901473721096301</v>
       </c>
       <c r="D58" s="0">
-        <v>1.3441313888461797</v>
+        <v>1.3442245467210197</v>
       </c>
       <c r="E58" s="0">
-        <v>1.099538209513103</v>
+        <v>1.0993537748570004</v>
       </c>
       <c r="F58" s="0">
-        <v>1.2763169553155331</v>
+        <v>1.2787255677704259</v>
       </c>
       <c r="G58" s="0">
-        <v>-0.024590486444361268</v>
+        <v>-0.025058159092035317</v>
       </c>
       <c r="H58" s="0">
-        <v>-0.038929076621422989</v>
+        <v>-0.039226192829312265</v>
       </c>
       <c r="I58" s="0">
-        <v>-0.085647358845379815</v>
+        <v>-0.086938754866829893</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.3255662713232199</v>
+        <v>1.3251230822890101</v>
       </c>
       <c r="B59" s="0">
-        <v>1.0575024458584501</v>
+        <v>1.0574981674735699</v>
       </c>
       <c r="C59" s="0">
-        <v>1.2048108240708</v>
+        <v>1.20105475784988</v>
       </c>
       <c r="D59" s="0">
-        <v>1.3567386400906056</v>
+        <v>1.356894159507676</v>
       </c>
       <c r="E59" s="0">
-        <v>1.1122718902593685</v>
+        <v>1.1121529494283493</v>
       </c>
       <c r="F59" s="0">
-        <v>1.2887449343690962</v>
+        <v>1.2913198571603899</v>
       </c>
       <c r="G59" s="0">
-        <v>-0.029884042773911646</v>
+        <v>-0.030495712379915101</v>
       </c>
       <c r="H59" s="0">
-        <v>-0.051731511662437772</v>
+        <v>-0.05193913334090406</v>
       </c>
       <c r="I59" s="0">
-        <v>-0.085178695242072777</v>
+        <v>-0.090691210242741224</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.33579811152603</v>
+        <v>1.3365479688962301</v>
       </c>
       <c r="B60" s="0">
-        <v>1.06764621794045</v>
+        <v>1.06734379395318</v>
       </c>
       <c r="C60" s="0">
-        <v>1.2128297732211699</v>
+        <v>1.21245176710019</v>
       </c>
       <c r="D60" s="0">
-        <v>1.3692678136437195</v>
+        <v>1.3694821554456704</v>
       </c>
       <c r="E60" s="0">
-        <v>1.1260189551861262</v>
+        <v>1.1259546574350192</v>
       </c>
       <c r="F60" s="0">
-        <v>1.3011107423043358</v>
+        <v>1.304009775655472</v>
       </c>
       <c r="G60" s="0">
-        <v>-0.032778690234466001</v>
+        <v>-0.032709361886211541</v>
       </c>
       <c r="H60" s="0">
-        <v>-0.058542041638468732</v>
+        <v>-0.058265093656824196</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.09003085362700522</v>
+        <v>-0.093699064317611228</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.3491195058371299</v>
+        <v>1.34990358106466</v>
       </c>
       <c r="B61" s="0">
-        <v>1.07653417188213</v>
+        <v>1.0786838811293</v>
       </c>
       <c r="C61" s="0">
-        <v>1.2044792908599</v>
+        <v>1.20491218206137</v>
       </c>
       <c r="D61" s="0">
-        <v>1.3823412055875042</v>
+        <v>1.3824437278795763</v>
       </c>
       <c r="E61" s="0">
-        <v>1.1400610325525002</v>
+        <v>1.1401560546528535</v>
       </c>
       <c r="F61" s="0">
-        <v>1.3131164083449274</v>
+        <v>1.3162946217524703</v>
       </c>
       <c r="G61" s="0">
-        <v>-0.034061850291704637</v>
+        <v>-0.033546519984413332</v>
       </c>
       <c r="H61" s="0">
-        <v>-0.063812526032653638</v>
+        <v>-0.063034204129353871</v>
       </c>
       <c r="I61" s="0">
-        <v>-0.10545163236281856</v>
+        <v>-0.10781183724244234</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.36130301119526</v>
+        <v>1.36018998034827</v>
       </c>
       <c r="B62" s="0">
-        <v>1.0875026348836401</v>
+        <v>1.0853972029047301</v>
       </c>
       <c r="C62" s="0">
-        <v>1.22585874331316</v>
+        <v>1.22871593286132</v>
       </c>
       <c r="D62" s="0">
-        <v>1.3951505599059673</v>
+        <v>1.3953239269501887</v>
       </c>
       <c r="E62" s="0">
-        <v>1.1545730399082863</v>
+        <v>1.1544620308282016</v>
       </c>
       <c r="F62" s="0">
-        <v>1.3258764792927014</v>
+        <v>1.3293072699390283</v>
       </c>
       <c r="G62" s="0">
-        <v>-0.0346417990426372</v>
+        <v>-0.03524665774649318</v>
       </c>
       <c r="H62" s="0">
-        <v>-0.067070838070718522</v>
+        <v>-0.067843806044552035</v>
       </c>
       <c r="I62" s="0">
-        <v>-0.1020509356788943</v>
+        <v>-0.1034593083906489</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.3695176127720901</v>
+        <v>1.3689039536565999</v>
       </c>
       <c r="B63" s="0">
-        <v>1.09803380968243</v>
+        <v>1.0978798527189</v>
       </c>
       <c r="C63" s="0">
-        <v>1.22793057225008</v>
+        <v>1.2257169102100001</v>
       </c>
       <c r="D63" s="0">
-        <v>1.4081148108341346</v>
+        <v>1.408326138174534</v>
       </c>
       <c r="E63" s="0">
-        <v>1.1693176909427803</v>
+        <v>1.1692945491598425</v>
       </c>
       <c r="F63" s="0">
-        <v>1.3382360214119167</v>
+        <v>1.3417762686219559</v>
       </c>
       <c r="G63" s="0">
-        <v>-0.03806752537603178</v>
+        <v>-0.038717330440928323</v>
       </c>
       <c r="H63" s="0">
-        <v>-0.070756830380856631</v>
+        <v>-0.071229942042304831</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.11113041718011632</v>
+        <v>-0.11620369220661585</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.38089492192831</v>
+        <v>1.3818334622331401</v>
       </c>
       <c r="B64" s="0">
-        <v>1.1118223369950799</v>
+        <v>1.1120168011165299</v>
       </c>
       <c r="C64" s="0">
-        <v>1.2239528440396501</v>
+        <v>1.2231357690706</v>
       </c>
       <c r="D64" s="0">
-        <v>1.4212430667376319</v>
+        <v>1.4215407582203345</v>
       </c>
       <c r="E64" s="0">
-        <v>1.1843800794711672</v>
+        <v>1.1844097889456804</v>
       </c>
       <c r="F64" s="0">
-        <v>1.3504554798451529</v>
+        <v>1.3542164283432685</v>
       </c>
       <c r="G64" s="0">
-        <v>-0.041219322485352261</v>
+        <v>-0.041044163020663472</v>
       </c>
       <c r="H64" s="0">
-        <v>-0.073518271321220963</v>
+        <v>-0.07361097254291224</v>
       </c>
       <c r="I64" s="0">
-        <v>-0.12385587471049321</v>
+        <v>-0.12872777319408846</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.39034554214304</v>
+        <v>1.3913139949876301</v>
       </c>
       <c r="B65" s="0">
-        <v>1.12420288973809</v>
+        <v>1.12333803105506</v>
       </c>
       <c r="C65" s="0">
-        <v>1.24784524446429</v>
+        <v>1.2466046694636399</v>
       </c>
       <c r="D65" s="0">
-        <v>1.4342301531565107</v>
+        <v>1.4346028652892486</v>
       </c>
       <c r="E65" s="0">
-        <v>1.1995591233683798</v>
+        <v>1.1995697871719604</v>
       </c>
       <c r="F65" s="0">
-        <v>1.3632777596018435</v>
+        <v>1.3671922728392416</v>
       </c>
       <c r="G65" s="0">
-        <v>-0.042347924630435546</v>
+        <v>-0.042431645872319644</v>
       </c>
       <c r="H65" s="0">
-        <v>-0.075350209410376942</v>
+        <v>-0.075857619731677497</v>
       </c>
       <c r="I65" s="0">
-        <v>-0.11646884117132233</v>
+        <v>-0.12104669797240955</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.4064743616933</v>
+        <v>1.4051279588047301</v>
       </c>
       <c r="B66" s="0">
-        <v>1.13767768414666</v>
+        <v>1.13820260765445</v>
       </c>
       <c r="C66" s="0">
-        <v>1.2630017791267301</v>
+        <v>1.26659352512579</v>
       </c>
       <c r="D66" s="0">
-        <v>1.4476927953220624</v>
+        <v>1.4478688389471828</v>
       </c>
       <c r="E66" s="0">
-        <v>1.2148809954982309</v>
+        <v>1.2150389250894957</v>
       </c>
       <c r="F66" s="0">
-        <v>1.3758347464063394</v>
+        <v>1.3800535170536403</v>
       </c>
       <c r="G66" s="0">
-        <v>-0.040157361139627624</v>
+        <v>-0.040765299675784308</v>
       </c>
       <c r="H66" s="0">
-        <v>-0.076270324332534806</v>
+        <v>-0.076278570212874749</v>
       </c>
       <c r="I66" s="0">
-        <v>-0.11389343512924105</v>
+        <v>-0.11544912768726941</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.4285047446619801</v>
+        <v>1.4278547804622399</v>
       </c>
       <c r="B67" s="0">
-        <v>1.1548372989835001</v>
+        <v>1.15448341362638</v>
       </c>
       <c r="C67" s="0">
-        <v>1.2655461958765</v>
+        <v>1.2644223603895199</v>
       </c>
       <c r="D67" s="0">
-        <v>1.4613156252621582</v>
+        <v>1.4616442405172714</v>
       </c>
       <c r="E67" s="0">
-        <v>1.2306803260572123</v>
+        <v>1.2307996761302782</v>
       </c>
       <c r="F67" s="0">
-        <v>1.3881288654250721</v>
+        <v>1.3923766000723279</v>
       </c>
       <c r="G67" s="0">
-        <v>-0.034411983663087904</v>
+        <v>-0.03528993780843262</v>
       </c>
       <c r="H67" s="0">
-        <v>-0.077061427859318826</v>
+        <v>-0.077082563385293359</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.12203752274378651</v>
+        <v>-0.12691029678147914</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.4430721796511901</v>
+        <v>1.4441238324886401</v>
       </c>
       <c r="B68" s="0">
-        <v>1.1651538714383001</v>
+        <v>1.1660665966899799</v>
       </c>
       <c r="C68" s="0">
-        <v>1.2712905517342601</v>
+        <v>1.2704563649692999</v>
       </c>
       <c r="D68" s="0">
-        <v>1.4748498532878105</v>
+        <v>1.4752104600898106</v>
       </c>
       <c r="E68" s="0">
-        <v>1.24659039308325</v>
+        <v>1.2468236586731112</v>
       </c>
       <c r="F68" s="0">
-        <v>1.4004729637846998</v>
+        <v>1.4048747437897851</v>
       </c>
       <c r="G68" s="0">
-        <v>-0.029775264739613477</v>
+        <v>-0.029637835895427279</v>
       </c>
       <c r="H68" s="0">
-        <v>-0.081613056585161325</v>
+        <v>-0.080775705345101062</v>
       </c>
       <c r="I68" s="0">
-        <v>-0.12858001155657275</v>
+        <v>-0.13364287947358808</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.46427941548091</v>
+        <v>1.4652945004709199</v>
       </c>
       <c r="B69" s="0">
-        <v>1.1753919046754999</v>
+        <v>1.17834829979764</v>
       </c>
       <c r="C69" s="0">
-        <v>1.2855800921398299</v>
+        <v>1.28691782129429</v>
       </c>
       <c r="D69" s="0">
-        <v>1.4887857784426339</v>
+        <v>1.48900340406085</v>
       </c>
       <c r="E69" s="0">
-        <v>1.2628844657098817</v>
+        <v>1.2632396702105384</v>
       </c>
       <c r="F69" s="0">
-        <v>1.412850460623299</v>
+        <v>1.4174621136209788</v>
       </c>
       <c r="G69" s="0">
-        <v>-0.025901738171352568</v>
+        <v>-0.025149016391807989</v>
       </c>
       <c r="H69" s="0">
-        <v>-0.08596147701339471</v>
+        <v>-0.085033339673330044</v>
       </c>
       <c r="I69" s="0">
-        <v>-0.12797473612412688</v>
+        <v>-0.13146837537042053</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.47978074101816</v>
+        <v>1.4782663329452399</v>
       </c>
       <c r="B70" s="0">
-        <v>1.1938271097170701</v>
+        <v>1.1899416284761799</v>
       </c>
       <c r="C70" s="0">
-        <v>1.2966292848379699</v>
+        <v>1.2966915329283399</v>
       </c>
       <c r="D70" s="0">
-        <v>1.5022246319234434</v>
+        <v>1.5026500132640384</v>
       </c>
       <c r="E70" s="0">
-        <v>1.2803050236767277</v>
+        <v>1.2802667512759707</v>
       </c>
       <c r="F70" s="0">
-        <v>1.4251735822635918</v>
+        <v>1.4298198375929623</v>
       </c>
       <c r="G70" s="0">
-        <v>-0.02427578588908447</v>
+        <v>-0.025534012198793907</v>
       </c>
       <c r="H70" s="0">
-        <v>-0.087006824060474233</v>
+        <v>-0.088955280777512497</v>
       </c>
       <c r="I70" s="0">
-        <v>-0.12805763564354028</v>
+        <v>-0.1327207303208856</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.4909632129432999</v>
+        <v>1.49042557842001</v>
       </c>
       <c r="B71" s="0">
-        <v>1.21072517501593</v>
+        <v>1.2104761605978001</v>
       </c>
       <c r="C71" s="0">
-        <v>1.3114470857665601</v>
+        <v>1.3109339324726701</v>
       </c>
       <c r="D71" s="0">
-        <v>1.5153479034050241</v>
+        <v>1.515748480329149</v>
       </c>
       <c r="E71" s="0">
-        <v>1.2983014824379489</v>
+        <v>1.2984570004261169</v>
       </c>
       <c r="F71" s="0">
-        <v>1.43754556417073</v>
+        <v>1.4423036336190778</v>
       </c>
       <c r="G71" s="0">
-        <v>-0.025688458827449141</v>
+        <v>-0.026860056842974028</v>
       </c>
       <c r="H71" s="0">
-        <v>-0.086987189574948789</v>
+        <v>-0.087658378671469431</v>
       </c>
       <c r="I71" s="0">
-        <v>-0.12602970165946223</v>
+        <v>-0.13123146328841553</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.49984367830329</v>
+        <v>1.5009008957147001</v>
       </c>
       <c r="B72" s="0">
-        <v>1.23182321356859</v>
+        <v>1.23322254998201</v>
       </c>
       <c r="C72" s="0">
-        <v>1.32565091485883</v>
+        <v>1.3251442663325901</v>
       </c>
       <c r="D72" s="0">
-        <v>1.5280252485606771</v>
+        <v>1.5284196451387022</v>
       </c>
       <c r="E72" s="0">
-        <v>1.3169759826827225</v>
+        <v>1.3173355123851829</v>
       </c>
       <c r="F72" s="0">
-        <v>1.4499061897028673</v>
+        <v>1.4547768639275183</v>
       </c>
       <c r="G72" s="0">
-        <v>-0.027491120843014614</v>
+        <v>-0.027334177279225901</v>
       </c>
       <c r="H72" s="0">
-        <v>-0.085402825102586011</v>
+        <v>-0.084437652340140959</v>
       </c>
       <c r="I72" s="0">
-        <v>-0.12568496873489785</v>
+        <v>-0.1311494636763289</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.5127370002359799</v>
+        <v>1.51377939323426</v>
       </c>
       <c r="B73" s="0">
-        <v>1.2521471493017999</v>
+        <v>1.25498972208854</v>
       </c>
       <c r="C73" s="0">
-        <v>1.3272525621612601</v>
+        <v>1.32590589119131</v>
       </c>
       <c r="D73" s="0">
-        <v>1.540958438620013</v>
+        <v>1.5412420483591041</v>
       </c>
       <c r="E73" s="0">
-        <v>1.3357570445288376</v>
+        <v>1.336202536279617</v>
       </c>
       <c r="F73" s="0">
-        <v>1.4618403166508949</v>
+        <v>1.4668027522409544</v>
       </c>
       <c r="G73" s="0">
-        <v>-0.028064233805626591</v>
+        <v>-0.027403139137105806</v>
       </c>
       <c r="H73" s="0">
-        <v>-0.085848574041994002</v>
+        <v>-0.085088333206476907</v>
       </c>
       <c r="I73" s="0">
-        <v>-0.13212884244517464</v>
+        <v>-0.13791720130328775</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>1.5258600212476701</v>
+        <v>1.5241260507235199</v>
       </c>
       <c r="B74" s="0">
-        <v>1.2632861356226699</v>
+        <v>1.25913989433427</v>
       </c>
       <c r="C74" s="0">
-        <v>1.3537103747399599</v>
+        <v>1.3554059892179799</v>
       </c>
       <c r="D74" s="0">
-        <v>1.554126013353007</v>
+        <v>1.5545569283282041</v>
       </c>
       <c r="E74" s="0">
-        <v>1.3544053611442488</v>
+        <v>1.354451093061821</v>
       </c>
       <c r="F74" s="0">
-        <v>1.4741183320819524</v>
+        <v>1.4791690418063141</v>
       </c>
       <c r="G74" s="0">
-        <v>-0.027815318419352135</v>
+        <v>-0.029030888766489338</v>
       </c>
       <c r="H74" s="0">
-        <v>-0.088715466337167898</v>
+        <v>-0.090832418470684489</v>
       </c>
       <c r="I74" s="0">
-        <v>-0.12174909790498824</v>
+        <v>-0.12579600220368234</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.5415101312302699</v>
+        <v>1.5412429887936401</v>
       </c>
       <c r="B75" s="0">
-        <v>1.2876029783588201</v>
+        <v>1.28734203605394</v>
       </c>
       <c r="C75" s="0">
-        <v>1.37221273372257</v>
+        <v>1.3721374566423901</v>
       </c>
       <c r="D75" s="0">
-        <v>1.5670571738330774</v>
+        <v>1.5674796546497856</v>
       </c>
       <c r="E75" s="0">
-        <v>1.3742790708297326</v>
+        <v>1.3745139082576336</v>
       </c>
       <c r="F75" s="0">
-        <v>1.4862108166521584</v>
+        <v>1.4912996839351147</v>
       </c>
       <c r="G75" s="0">
-        <v>-0.024828164718523529</v>
+        <v>-0.025786157479012382</v>
       </c>
       <c r="H75" s="0">
-        <v>-0.086932053609167032</v>
+        <v>-0.087762382461250871</v>
       </c>
       <c r="I75" s="0">
-        <v>-0.11445154998984147</v>
+        <v>-0.11930422249307195</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>1.55867107367192</v>
+        <v>1.55965805245959</v>
       </c>
       <c r="B76" s="0">
-        <v>1.30915037387235</v>
+        <v>1.3108994649197701</v>
       </c>
       <c r="C76" s="0">
-        <v>1.38660259672222</v>
+        <v>1.38674098535066</v>
       </c>
       <c r="D76" s="0">
-        <v>1.5802827909965591</v>
+        <v>1.5806933934469194</v>
       </c>
       <c r="E76" s="0">
-        <v>1.3947300670855143</v>
+        <v>1.3951406823013881</v>
       </c>
       <c r="F76" s="0">
-        <v>1.4981059994410211</v>
+        <v>1.503275027465919</v>
       </c>
       <c r="G76" s="0">
-        <v>-0.021603435640952313</v>
+        <v>-0.021309109236765548</v>
       </c>
       <c r="H76" s="0">
-        <v>-0.084564051298323353</v>
+        <v>-0.084130612523940856</v>
       </c>
       <c r="I76" s="0">
-        <v>-0.11096644994413357</v>
+        <v>-0.11615394549385349</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>1.5818625672665501</v>
+        <v>1.5828782652768001</v>
       </c>
       <c r="B77" s="0">
-        <v>1.33528068641355</v>
+        <v>1.33428884889031</v>
       </c>
       <c r="C77" s="0">
-        <v>1.4080701798435</v>
+        <v>1.4064093206037001</v>
       </c>
       <c r="D77" s="0">
-        <v>1.5932362159627551</v>
+        <v>1.5937656021982376</v>
       </c>
       <c r="E77" s="0">
-        <v>1.415911745108144</v>
+        <v>1.4161893254299092</v>
       </c>
       <c r="F77" s="0">
-        <v>1.5101295247411242</v>
+        <v>1.5152844181332978</v>
       </c>
       <c r="G77" s="0">
-        <v>-0.022654258587900305</v>
+        <v>-0.022831443588797212</v>
       </c>
       <c r="H77" s="0">
-        <v>-0.082294125527788003</v>
+        <v>-0.083039026339524549</v>
       </c>
       <c r="I77" s="0">
-        <v>-0.10257611878279022</v>
+        <v>-0.10901289033149658</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>1.5579343668215999</v>
+        <v>1.55602003501801</v>
       </c>
       <c r="B78" s="0">
-        <v>1.35293583018199</v>
+        <v>1.35235033097584</v>
       </c>
       <c r="C78" s="0">
-        <v>1.42767164595096</v>
+        <v>1.4285906284527199</v>
       </c>
       <c r="D78" s="0">
-        <v>1.6043952932232828</v>
+        <v>1.604764780572848</v>
       </c>
       <c r="E78" s="0">
-        <v>1.4374202908692688</v>
+        <v>1.4377595513965788</v>
       </c>
       <c r="F78" s="0">
-        <v>1.5223003020992756</v>
+        <v>1.5275733252671573</v>
       </c>
       <c r="G78" s="0">
-        <v>-0.035881241653738911</v>
+        <v>-0.037015893345915825</v>
       </c>
       <c r="H78" s="0">
-        <v>-0.084149359165451368</v>
+        <v>-0.085066421217923446</v>
       </c>
       <c r="I78" s="0">
-        <v>-0.092964507582988326</v>
+        <v>-0.097693554879700731</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.57725478498591</v>
+        <v>1.57727048133451</v>
       </c>
       <c r="B79" s="0">
-        <v>1.37916339800891</v>
+        <v>1.37907068769675</v>
       </c>
       <c r="C79" s="0">
-        <v>1.4701939519578799</v>
+        <v>1.4705885621696599</v>
       </c>
       <c r="D79" s="0">
-        <v>1.6175060973047009</v>
+        <v>1.6179890358511668</v>
       </c>
       <c r="E79" s="0">
-        <v>1.4588274207487211</v>
+        <v>1.4592028852393921</v>
       </c>
       <c r="F79" s="0">
-        <v>1.5345947604248813</v>
+        <v>1.53986664549482</v>
       </c>
       <c r="G79" s="0">
-        <v>-0.039107103967811634</v>
+        <v>-0.039966109705786582</v>
       </c>
       <c r="H79" s="0">
-        <v>-0.078812284866872057</v>
+        <v>-0.078952454655457346</v>
       </c>
       <c r="I79" s="0">
-        <v>-0.065255093709971818</v>
+        <v>-0.070008053890973698</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>1.5971047101623199</v>
+        <v>1.5980048540113301</v>
       </c>
       <c r="B80" s="0">
-        <v>1.41149836398978</v>
+        <v>1.4132533923350901</v>
       </c>
       <c r="C80" s="0">
-        <v>1.5053485717861701</v>
+        <v>1.5060581515834099</v>
       </c>
       <c r="D80" s="0">
-        <v>1.6308990497963642</v>
+        <v>1.6313378702538512</v>
       </c>
       <c r="E80" s="0">
-        <v>1.4806386548193682</v>
+        <v>1.481168403078011</v>
       </c>
       <c r="F80" s="0">
-        <v>1.5467641721537819</v>
+        <v>1.5520856560529572</v>
       </c>
       <c r="G80" s="0">
-        <v>-0.035733914051810617</v>
+        <v>-0.035502371691595841</v>
       </c>
       <c r="H80" s="0">
-        <v>-0.071236656857596933</v>
+        <v>-0.070239977558488681</v>
       </c>
       <c r="I80" s="0">
-        <v>-0.041983355988889456</v>
+        <v>-0.046477380663110406</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>1.6089675199354001</v>
+        <v>1.60993305975353</v>
       </c>
       <c r="B81" s="0">
-        <v>1.43093875155173</v>
+        <v>1.43317037320872</v>
       </c>
       <c r="C81" s="0">
-        <v>1.52719618697718</v>
+        <v>1.52825400631096</v>
       </c>
       <c r="D81" s="0">
-        <v>1.6445272190719753</v>
+        <v>1.6448873185317034</v>
       </c>
       <c r="E81" s="0">
-        <v>1.5021630716084935</v>
+        <v>1.5027066860255158</v>
       </c>
       <c r="F81" s="0">
-        <v>1.5587036599619768</v>
+        <v>1.5640721850685024</v>
       </c>
       <c r="G81" s="0">
-        <v>-0.035631274269710425</v>
+        <v>-0.035193189622256725</v>
       </c>
       <c r="H81" s="0">
-        <v>-0.0688683829306658</v>
+        <v>-0.068408333047039457</v>
       </c>
       <c r="I81" s="0">
-        <v>-0.031522606556990462</v>
+        <v>-0.036223800910288782</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>1.6218788822326999</v>
+        <v>1.6198615529984299</v>
       </c>
       <c r="B82" s="0">
-        <v>1.46206365357587</v>
+        <v>1.4581000769938901</v>
       </c>
       <c r="C82" s="0">
-        <v>1.54554164045524</v>
+        <v>1.54278063396795</v>
       </c>
       <c r="D82" s="0">
-        <v>1.6577976665543748</v>
+        <v>1.6583360654737815</v>
       </c>
       <c r="E82" s="0">
-        <v>1.5246149452772708</v>
+        <v>1.5247915842338684</v>
       </c>
       <c r="F82" s="0">
-        <v>1.5707931287903303</v>
+        <v>1.5760424573485914</v>
       </c>
       <c r="G82" s="0">
-        <v>-0.035825624042701357</v>
+        <v>-0.037442623951786144</v>
       </c>
       <c r="H82" s="0">
-        <v>-0.063356360893946889</v>
+        <v>-0.065706746581515027</v>
       </c>
       <c r="I82" s="0">
-        <v>-0.025319291983383597</v>
+        <v>-0.032781187273211145</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>1.6334034597639899</v>
+        <v>1.6336451788750599</v>
       </c>
       <c r="B83" s="0">
-        <v>1.48975783219646</v>
+        <v>1.48987660319217</v>
       </c>
       <c r="C83" s="0">
-        <v>1.56197288089474</v>
+        <v>1.5628770125056699</v>
       </c>
       <c r="D83" s="0">
-        <v>1.6714240227348218</v>
+        <v>1.6719258322059911</v>
       </c>
       <c r="E83" s="0">
-        <v>1.5470222093114374</v>
+        <v>1.5474152321849433</v>
       </c>
       <c r="F83" s="0">
-        <v>1.5828646303095624</v>
+        <v>1.588210557807793</v>
       </c>
       <c r="G83" s="0">
-        <v>-0.036580848694569908</v>
+        <v>-0.037493900922228325</v>
       </c>
       <c r="H83" s="0">
-        <v>-0.058446471087718083</v>
+        <v>-0.059055807862279076</v>
       </c>
       <c r="I83" s="0">
-        <v>-0.020245414691296388</v>
+        <v>-0.025029351179596166</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>1.6489594454266601</v>
+        <v>1.6498486686373901</v>
       </c>
       <c r="B84" s="0">
-        <v>1.51444819291835</v>
+        <v>1.51622118197807</v>
       </c>
       <c r="C84" s="0">
-        <v>1.58623028848825</v>
+        <v>1.58716654801049</v>
       </c>
       <c r="D84" s="0">
-        <v>1.6856811404331629</v>
+        <v>1.6861317716382682</v>
       </c>
       <c r="E84" s="0">
-        <v>1.5691772397232742</v>
+        <v>1.569755687619252</v>
       </c>
       <c r="F84" s="0">
-        <v>1.5950312164259743</v>
+        <v>1.6003951436726984</v>
       </c>
       <c r="G84" s="0">
-        <v>-0.036328378536846929</v>
+        <v>-0.03606643178616651</v>
       </c>
       <c r="H84" s="0">
-        <v>-0.053493028667418986</v>
+        <v>-0.052642737750726747</v>
       </c>
       <c r="I84" s="0">
-        <v>-0.0092495823312850316</v>
+        <v>-0.013674931504772524</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>1.6671645204110701</v>
+        <v>1.6679617240153899</v>
       </c>
       <c r="B85" s="0">
-        <v>1.54688657513751</v>
+        <v>1.5486256810007999</v>
       </c>
       <c r="C85" s="0">
-        <v>1.61086504978125</v>
+        <v>1.61049019971118</v>
       </c>
       <c r="D85" s="0">
-        <v>1.6999872779296992</v>
+        <v>1.700390877925442</v>
       </c>
       <c r="E85" s="0">
-        <v>1.5918502722288708</v>
+        <v>1.5924142926345701</v>
       </c>
       <c r="F85" s="0">
-        <v>1.6072524095012526</v>
+        <v>1.6125929619058199</v>
       </c>
       <c r="G85" s="0">
-        <v>-0.03156625373643604</v>
+        <v>-0.031314040998780351</v>
       </c>
       <c r="H85" s="0">
-        <v>-0.043992767186879361</v>
+        <v>-0.043843118899569933</v>
       </c>
       <c r="I85" s="0">
-        <v>0.0036981623585308583</v>
+        <v>-0.0020075028787836444</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>1.69286623850083</v>
+        <v>1.69084299300411</v>
       </c>
       <c r="B86" s="0">
-        <v>1.5851714771568901</v>
+        <v>1.58139671527604</v>
       </c>
       <c r="C86" s="0">
-        <v>1.6389913729777801</v>
+        <v>1.6371653656795899</v>
       </c>
       <c r="D86" s="0">
-        <v>1.7144520252159821</v>
+        <v>1.7149897974222996</v>
       </c>
       <c r="E86" s="0">
-        <v>1.614791599964313</v>
+        <v>1.6150350083261624</v>
       </c>
       <c r="F86" s="0">
-        <v>1.619564229188323</v>
+        <v>1.624818953853614</v>
       </c>
       <c r="G86" s="0">
-        <v>-0.020851515959487799</v>
+        <v>-0.022435828899848711</v>
       </c>
       <c r="H86" s="0">
-        <v>-0.032352258091080707</v>
+        <v>-0.034602014792851944</v>
       </c>
       <c r="I86" s="0">
-        <v>0.019761242739538918</v>
+        <v>0.012921139835123545</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>1.7195769506076599</v>
+        <v>1.72001401090748</v>
       </c>
       <c r="B87" s="0">
-        <v>1.6079608592808901</v>
+        <v>1.60857586545749</v>
       </c>
       <c r="C87" s="0">
-        <v>1.6685132689637201</v>
+        <v>1.66986041664887</v>
       </c>
       <c r="D87" s="0">
-        <v>1.7296297178353646</v>
+        <v>1.7301260935430698</v>
       </c>
       <c r="E87" s="0">
-        <v>1.6368030365048472</v>
+        <v>1.6372733827242989</v>
       </c>
       <c r="F87" s="0">
-        <v>1.6317402564851045</v>
+        <v>1.6370560708823727</v>
       </c>
       <c r="G87" s="0">
-        <v>-0.011381229186325278</v>
+        <v>-0.012114214631299396</v>
       </c>
       <c r="H87" s="0">
-        <v>-0.027121181880616688</v>
+        <v>-0.027513156554962396</v>
       </c>
       <c r="I87" s="0">
-        <v>0.03632409549115681</v>
+        <v>0.032038921801993553</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>1.73876552187888</v>
+        <v>1.7396311861863401</v>
       </c>
       <c r="B88" s="0">
-        <v>1.63758798345579</v>
+        <v>1.6391269698805799</v>
       </c>
       <c r="C88" s="0">
-        <v>1.69392752243158</v>
+        <v>1.6946983073928901</v>
       </c>
       <c r="D88" s="0">
-        <v>1.7442206502994779</v>
+        <v>1.7446922967933278</v>
       </c>
       <c r="E88" s="0">
-        <v>1.6592227473845351</v>
+        <v>1.659816451864911</v>
       </c>
       <c r="F88" s="0">
-        <v>1.6439225149945149</v>
+        <v>1.6492132276039553</v>
       </c>
       <c r="G88" s="0">
-        <v>-0.0039663048357289577</v>
+        <v>-0.0037259708107718935</v>
       </c>
       <c r="H88" s="0">
-        <v>-0.021972966964500559</v>
+        <v>-0.021318850611045694</v>
       </c>
       <c r="I88" s="0">
-        <v>0.050329805764576081</v>
+        <v>0.046184918622974358</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>1.7621541004652901</v>
+        <v>1.7627466374903999</v>
       </c>
       <c r="B89" s="0">
-        <v>1.6637350768986501</v>
+        <v>1.6649971762865501</v>
       </c>
       <c r="C89" s="0">
-        <v>1.7195457218015899</v>
+        <v>1.7215038678929699</v>
       </c>
       <c r="D89" s="0">
-        <v>1.7590891901123442</v>
+        <v>1.7594987929647536</v>
       </c>
       <c r="E89" s="0">
-        <v>1.6814081964770897</v>
+        <v>1.6819692524054655</v>
       </c>
       <c r="F89" s="0">
-        <v>1.6560151099461311</v>
+        <v>1.6613198821287816</v>
       </c>
       <c r="G89" s="0">
-        <v>0.0025746582343173837</v>
+        <v>0.0026983212645539474</v>
       </c>
       <c r="H89" s="0">
-        <v>-0.017936336380493394</v>
+        <v>-0.017973979769803791</v>
       </c>
       <c r="I89" s="0">
-        <v>0.063470998933874034</v>
+        <v>0.059338769290126221</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>1.7802139697756001</v>
+        <v>1.7782408561488401</v>
       </c>
       <c r="B90" s="0">
-        <v>1.6868600081753899</v>
+        <v>1.6833809335646801</v>
       </c>
       <c r="C90" s="0">
-        <v>1.73984129359393</v>
+        <v>1.7355477681172899</v>
       </c>
       <c r="D90" s="0">
-        <v>1.7737995723227431</v>
+        <v>1.7743665787121381</v>
       </c>
       <c r="E90" s="0">
-        <v>1.7033939544010333</v>
+        <v>1.703672123218686</v>
       </c>
       <c r="F90" s="0">
-        <v>1.6679472561774349</v>
+        <v>1.6730477012352716</v>
       </c>
       <c r="G90" s="0">
-        <v>0.0064831484720194524</v>
+        <v>0.0047906969387545694</v>
       </c>
       <c r="H90" s="0">
-        <v>-0.01611197886776547</v>
+        <v>-0.018335512844208771</v>
       </c>
       <c r="I90" s="0">
-        <v>0.071519398374208412</v>
+        <v>0.063173306697391865</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>1.7978217467426201</v>
+        <v>1.7984431010141599</v>
       </c>
       <c r="B91" s="0">
-        <v>1.70971429720518</v>
+        <v>1.7105655209711099</v>
       </c>
       <c r="C91" s="0">
-        <v>1.7512715301680599</v>
+        <v>1.75286247831519</v>
       </c>
       <c r="D91" s="0">
-        <v>1.7882853896079358</v>
+        <v>1.7887779847481724</v>
       </c>
       <c r="E91" s="0">
-        <v>1.7252964998145464</v>
+        <v>1.7258156834137561</v>
       </c>
       <c r="F91" s="0">
-        <v>1.6796306688809901</v>
+        <v>1.6848411485840549</v>
       </c>
       <c r="G91" s="0">
-        <v>0.0082712372285719607</v>
+        <v>0.0077067911109691273</v>
       </c>
       <c r="H91" s="0">
-        <v>-0.015719328165656681</v>
+        <v>-0.015946696493167673</v>
       </c>
       <c r="I91" s="0">
-        <v>0.072425919244556575</v>
+        <v>0.068115150471061509</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>1.8092902875281001</v>
+        <v>1.810178610908</v>
       </c>
       <c r="B92" s="0">
-        <v>1.72993096628698</v>
+        <v>1.73140251479142</v>
       </c>
       <c r="C92" s="0">
-        <v>1.7637617653473401</v>
+        <v>1.76438489663305</v>
       </c>
       <c r="D92" s="0">
-        <v>1.8022266142973293</v>
+        <v>1.8026960278667785</v>
       </c>
       <c r="E92" s="0">
-        <v>1.7470307868536743</v>
+        <v>1.7476465452459031</v>
       </c>
       <c r="F92" s="0">
-        <v>1.6912733468846026</v>
+        <v>1.6964297914216793</v>
       </c>
       <c r="G92" s="0">
-        <v>0.0076887131410500803</v>
+        <v>0.0079563508565037057</v>
       </c>
       <c r="H92" s="0">
-        <v>-0.017585962532026503</v>
+        <v>-0.016995835027596384</v>
       </c>
       <c r="I92" s="0">
-        <v>0.070628041714232634</v>
+        <v>0.066444239327231119</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>1.8211593656465499</v>
+        <v>1.82141183624025</v>
       </c>
       <c r="B93" s="0">
-        <v>1.7459085910826999</v>
+        <v>1.74688122231879</v>
       </c>
       <c r="C93" s="0">
-        <v>1.75716408163725</v>
+        <v>1.75840965792801</v>
       </c>
       <c r="D93" s="0">
-        <v>1.8162967851467113</v>
+        <v>1.8167039615632483</v>
       </c>
       <c r="E93" s="0">
-        <v>1.7682638890236342</v>
+        <v>1.7688284300907728</v>
       </c>
       <c r="F93" s="0">
-        <v>1.7022280286136056</v>
+        <v>1.7073654367676414</v>
       </c>
       <c r="G93" s="0">
-        <v>0.0050384957132944726</v>
+        <v>0.0049951305021878828</v>
       </c>
       <c r="H93" s="0">
-        <v>-0.022909421345097002</v>
+        <v>-0.023158870570527818</v>
       </c>
       <c r="I93" s="0">
-        <v>0.056826269052073351</v>
+        <v>0.052367795274215069</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>1.83300878030933</v>
+        <v>1.8311487553180901</v>
       </c>
       <c r="B94" s="0">
-        <v>1.7607217101455701</v>
+        <v>1.7573626082573</v>
       </c>
       <c r="C94" s="0">
-        <v>1.7723264495158899</v>
+        <v>1.7688488533011699</v>
       </c>
       <c r="D94" s="0">
-        <v>1.8300786046158422</v>
+        <v>1.8306411978263815</v>
       </c>
       <c r="E94" s="0">
-        <v>1.7893763851322995</v>
+        <v>1.789674388432247</v>
       </c>
       <c r="F94" s="0">
-        <v>1.7133581733505572</v>
+        <v>1.7183081298132772</v>
       </c>
       <c r="G94" s="0">
-        <v>0.0033676137634432836</v>
+        <v>0.0017326054307417243</v>
       </c>
       <c r="H94" s="0">
-        <v>-0.02720489934209698</v>
+        <v>-0.029367657131290536</v>
       </c>
       <c r="I94" s="0">
-        <v>0.058666686500815295</v>
+        <v>0.051050299596690094</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>1.8491831405266601</v>
+        <v>1.8501221989929999</v>
       </c>
       <c r="B95" s="0">
-        <v>1.78536032281903</v>
+        <v>1.78636073434644</v>
       </c>
       <c r="C95" s="0">
-        <v>1.7920445779722101</v>
+        <v>1.79351829073922</v>
       </c>
       <c r="D95" s="0">
-        <v>1.8434180092022414</v>
+        <v>1.8439228209915854</v>
       </c>
       <c r="E95" s="0">
-        <v>1.8109668656139537</v>
+        <v>1.8115019675038653</v>
       </c>
       <c r="F95" s="0">
-        <v>1.7243051877171203</v>
+        <v>1.7293286956948546</v>
       </c>
       <c r="G95" s="0">
-        <v>0.0045729174759907521</v>
+        <v>0.0041230461156218506</v>
       </c>
       <c r="H95" s="0">
-        <v>-0.026429257723403637</v>
+        <v>-0.02657124870155702</v>
       </c>
       <c r="I95" s="0">
-        <v>0.067296826501884441</v>
+        <v>0.063196369010914064</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>1.86254055310289</v>
+        <v>1.8632471139469899</v>
       </c>
       <c r="B96" s="0">
-        <v>1.8076851626288899</v>
+        <v>1.8090526328066401</v>
       </c>
       <c r="C96" s="0">
-        <v>1.8098691819182899</v>
+        <v>1.8104622957177701</v>
       </c>
       <c r="D96" s="0">
-        <v>1.85643677623925</v>
+        <v>1.8568909648770968</v>
       </c>
       <c r="E96" s="0">
-        <v>1.8325015071332531</v>
+        <v>1.8331277615335462</v>
       </c>
       <c r="F96" s="0">
-        <v>1.7348773749097359</v>
+        <v>1.7398402435924465</v>
       </c>
       <c r="G96" s="0">
-        <v>0.005779503213798518</v>
+        <v>0.0059975459895138519</v>
       </c>
       <c r="H96" s="0">
-        <v>-0.024339503759027326</v>
+        <v>-0.02378541974728119</v>
       </c>
       <c r="I96" s="0">
-        <v>0.07542769712262784</v>
+        <v>0.071213516861524467</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>1.8786368730323599</v>
+        <v>1.8786726143566601</v>
       </c>
       <c r="B97" s="0">
-        <v>1.83395174493084</v>
+        <v>1.8349530112657899</v>
       </c>
       <c r="C97" s="0">
-        <v>1.83272378491809</v>
+        <v>1.8326528173415499</v>
       </c>
       <c r="D97" s="0">
-        <v>1.8689078778072392</v>
+        <v>1.8692993724538374</v>
       </c>
       <c r="E97" s="0">
-        <v>1.8543254889219098</v>
+        <v>1.8548999309217926</v>
       </c>
       <c r="F97" s="0">
-        <v>1.745288974561976</v>
+        <v>1.7501916517155991</v>
       </c>
       <c r="G97" s="0">
-        <v>0.0085047140369633404</v>
+        <v>0.0083527483290433604</v>
       </c>
       <c r="H97" s="0">
-        <v>-0.018403841843665197</v>
+        <v>-0.018723507437300693</v>
       </c>
       <c r="I97" s="0">
-        <v>0.086976446913491559</v>
+        <v>0.081869690958635499</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>1.8944184267512401</v>
+        <v>1.8926611183741</v>
       </c>
       <c r="B98" s="0">
-        <v>1.8701063534227</v>
+        <v>1.8667259957181099</v>
       </c>
       <c r="C98" s="0">
-        <v>1.85100850949886</v>
+        <v>1.8490793062655499</v>
       </c>
       <c r="D98" s="0">
-        <v>1.8803594356979105</v>
+        <v>1.8809013024289201</v>
       </c>
       <c r="E98" s="0">
-        <v>1.8766284804162157</v>
+        <v>1.8769282653301651</v>
       </c>
       <c r="F98" s="0">
-        <v>1.7554392570186264</v>
+        <v>1.7602011275215492</v>
       </c>
       <c r="G98" s="0">
-        <v>0.012993506493618939</v>
+        <v>0.011467585196388786</v>
       </c>
       <c r="H98" s="0">
-        <v>-0.0094623402547688203</v>
+        <v>-0.011575390495569261</v>
       </c>
       <c r="I98" s="0">
-        <v>0.096198655633957686</v>
+        <v>0.08978384961644334</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>1.9050894340172499</v>
+        <v>1.90626829481778</v>
       </c>
       <c r="B99" s="0">
-        <v>1.8900587837001701</v>
+        <v>1.89102817198101</v>
       </c>
       <c r="C99" s="0">
-        <v>1.86937230485016</v>
+        <v>1.8703866010252801</v>
       </c>
       <c r="D99" s="0">
-        <v>1.8916619140566924</v>
+        <v>1.8921747989006679</v>
       </c>
       <c r="E99" s="0">
-        <v>1.8977689519819247</v>
+        <v>1.8982910550828105</v>
       </c>
       <c r="F99" s="0">
-        <v>1.7651957286406967</v>
+        <v>1.7699666743843099</v>
       </c>
       <c r="G99" s="0">
-        <v>0.013448536119488699</v>
+        <v>0.013051518313775361</v>
       </c>
       <c r="H99" s="0">
-        <v>-0.0073486140276919111</v>
+        <v>-0.0075317499552098278</v>
       </c>
       <c r="I99" s="0">
-        <v>0.10337063574140352</v>
+        <v>0.099356492640154156</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>1.91118836521184</v>
+        <v>1.9117248845525801</v>
       </c>
       <c r="B100" s="0">
-        <v>1.91194691395478</v>
+        <v>1.9133382681179401</v>
       </c>
       <c r="C100" s="0">
-        <v>1.8788590783102801</v>
+        <v>1.8796672465589499</v>
       </c>
       <c r="D100" s="0">
-        <v>1.9025076277754109</v>
+        <v>1.9029402517602612</v>
       </c>
       <c r="E100" s="0">
-        <v>1.9185734462122841</v>
+        <v>1.9191896354824243</v>
       </c>
       <c r="F100" s="0">
-        <v>1.7744470162572741</v>
+        <v>1.7791634833223153</v>
       </c>
       <c r="G100" s="0">
-        <v>0.011708254223655968</v>
+        <v>0.011914017660140984</v>
       </c>
       <c r="H100" s="0">
-        <v>-0.0064484127137387675</v>
+        <v>-0.0059248111151295243</v>
       </c>
       <c r="I100" s="0">
-        <v>0.10486455881346873</v>
+        <v>0.10144619455871497</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>1.9281795011226499</v>
+        <v>1.9281509450072201</v>
       </c>
       <c r="B101" s="0">
-        <v>1.93601846337465</v>
+        <v>1.93701705491931</v>
       </c>
       <c r="C101" s="0">
-        <v>1.8940579834662401</v>
+        <v>1.8973626562731301</v>
       </c>
       <c r="D101" s="0">
-        <v>1.9134792195615957</v>
+        <v>1.913825994934115</v>
       </c>
       <c r="E101" s="0">
-        <v>1.939175171970418</v>
+        <v>1.939737030032598</v>
       </c>
       <c r="F101" s="0">
-        <v>1.7834027306132922</v>
+        <v>1.7881241758811741</v>
       </c>
       <c r="G101" s="0">
-        <v>0.012738072683437756</v>
+        <v>0.012658725464693463</v>
       </c>
       <c r="H101" s="0">
-        <v>-0.0022697032326057958</v>
+        <v>-0.0024262670199936185</v>
       </c>
       <c r="I101" s="0">
-        <v>0.11097231716776552</v>
+        <v>0.10844419985323059</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>1.9387669055109999</v>
+        <v>1.9370528099086199</v>
       </c>
       <c r="B102" s="0">
-        <v>1.9663525976470699</v>
+        <v>1.96307357374842</v>
       </c>
       <c r="C102" s="0">
-        <v>1.91333037798184</v>
+        <v>1.9084402718094899</v>
       </c>
       <c r="D102" s="0">
-        <v>1.9234740898862259</v>
+        <v>1.9240285155458257</v>
       </c>
       <c r="E102" s="0">
-        <v>1.9600902760089718</v>
+        <v>1.9603662138442799</v>
       </c>
       <c r="F102" s="0">
-        <v>1.7922349528318775</v>
+        <v>1.7966692006913034</v>
       </c>
       <c r="G102" s="0">
-        <v>0.014876500718505686</v>
+        <v>0.013256507013571351</v>
       </c>
       <c r="H102" s="0">
-        <v>0.0060251210893690326</v>
+        <v>0.0038955600503615554</v>
       </c>
       <c r="I102" s="0">
-        <v>0.12039886944721288</v>
+        <v>0.11224637302098946</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>1.9500897740977099</v>
+        <v>1.9513449476887701</v>
       </c>
       <c r="B103" s="0">
-        <v>1.9958691013151599</v>
+        <v>1.99673051601137</v>
       </c>
       <c r="C103" s="0">
-        <v>1.92441299756939</v>
+        <v>1.9246970564703401</v>
       </c>
       <c r="D103" s="0">
-        <v>1.9330921607808398</v>
+        <v>1.9335932239707276</v>
       </c>
       <c r="E103" s="0">
-        <v>1.9807645780808065</v>
+        <v>1.9812635923818109</v>
       </c>
       <c r="F103" s="0">
-        <v>1.8005729875512537</v>
+        <v>1.8050643283081473</v>
       </c>
       <c r="G103" s="0">
-        <v>0.017035292347064652</v>
+        <v>0.016668056373128171</v>
       </c>
       <c r="H103" s="0">
-        <v>0.015612802458217953</v>
+        <v>0.015391523188534977</v>
       </c>
       <c r="I103" s="0">
-        <v>0.12451638820689705</v>
+        <v>0.11983551422521772</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>1.9625479649148001</v>
+        <v>1.9629835143361101</v>
       </c>
       <c r="B104" s="0">
-        <v>2.0286815338440398</v>
+        <v>2.0300194487130998</v>
       </c>
       <c r="C104" s="0">
-        <v>1.9388092459428601</v>
+        <v>1.9399119191279299</v>
       </c>
       <c r="D104" s="0">
-        <v>1.9420890865214242</v>
+        <v>1.9424870268885792</v>
       </c>
       <c r="E104" s="0">
-        <v>2.0012482949042876</v>
+        <v>2.0018466498122618</v>
       </c>
       <c r="F104" s="0">
-        <v>1.8087267881155895</v>
+        <v>1.8131780781682125</v>
       </c>
       <c r="G104" s="0">
-        <v>0.019898818470470338</v>
+        <v>0.020118702353525128</v>
       </c>
       <c r="H104" s="0">
-        <v>0.026369844246289822</v>
+        <v>0.026902604952604495</v>
       </c>
       <c r="I104" s="0">
-        <v>0.12942860130823464</v>
+        <v>0.12627287134426857</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>1.9698410647367199</v>
+        <v>1.9699131241457899</v>
       </c>
       <c r="B105" s="0">
-        <v>2.0551660732955601</v>
+        <v>2.056182353609</v>
       </c>
       <c r="C105" s="0">
-        <v>1.9436123462263499</v>
+        <v>1.94564345167756</v>
       </c>
       <c r="D105" s="0">
-        <v>1.9507868139536673</v>
+        <v>1.9511112748629289</v>
       </c>
       <c r="E105" s="0">
-        <v>2.0209208493573785</v>
+        <v>2.0214634442922694</v>
       </c>
       <c r="F105" s="0">
-        <v>1.8163248538147152</v>
+        <v>1.8207315628335845</v>
       </c>
       <c r="G105" s="0">
-        <v>0.020496048367155163</v>
+        <v>0.020405997520798563</v>
       </c>
       <c r="H105" s="0">
-        <v>0.034192649486942443</v>
+        <v>0.034061949409054354</v>
       </c>
       <c r="I105" s="0">
-        <v>0.1274010140023128</v>
+        <v>0.12444540630804028</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>1.9805279035855501</v>
+        <v>1.97879048892985</v>
       </c>
       <c r="B106" s="0">
-        <v>2.0819039397615402</v>
+        <v>2.0789101697500598</v>
       </c>
       <c r="C106" s="0">
-        <v>1.94995190890321</v>
+        <v>1.9468427848249501</v>
       </c>
       <c r="D106" s="0">
-        <v>1.9593117100985968</v>
+        <v>1.9597782040908267</v>
       </c>
       <c r="E106" s="0">
-        <v>2.040017936066747</v>
+        <v>2.0402937155638172</v>
       </c>
       <c r="F106" s="0">
-        <v>1.8235629493641172</v>
+        <v>1.8277495805943802</v>
       </c>
       <c r="G106" s="0">
-        <v>0.021233350424686531</v>
+        <v>0.019819848946615936</v>
       </c>
       <c r="H106" s="0">
-        <v>0.042318554166436553</v>
+        <v>0.040379402256719703</v>
       </c>
       <c r="I106" s="0">
-        <v>0.12652060206946944</v>
+        <v>0.11980730528448236</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>1.9908833470473299</v>
+        <v>1.9920228810765199</v>
       </c>
       <c r="B107" s="0">
-        <v>2.11203227141886</v>
+        <v>2.11247563265536</v>
       </c>
       <c r="C107" s="0">
-        <v>1.96181462777939</v>
+        <v>1.9612024658723699</v>
       </c>
       <c r="D107" s="0">
-        <v>1.9673164746210148</v>
+        <v>1.967767560560105</v>
       </c>
       <c r="E107" s="0">
-        <v>2.0588439027397829</v>
+        <v>2.0592851529330605</v>
       </c>
       <c r="F107" s="0">
-        <v>1.8305634380165956</v>
+        <v>1.8347346508839182</v>
       </c>
       <c r="G107" s="0">
-        <v>0.023535740575854541</v>
+        <v>0.023288701502436816</v>
       </c>
       <c r="H107" s="0">
-        <v>0.053245444575809167</v>
+        <v>0.05278012921385556</v>
       </c>
       <c r="I107" s="0">
-        <v>0.13149740495251028</v>
+        <v>0.12667832866178244</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>2.0025793471240001</v>
+        <v>2.0030819834939599</v>
       </c>
       <c r="B108" s="0">
-        <v>2.1439932090554601</v>
+        <v>2.14546189952368</v>
       </c>
       <c r="C108" s="0">
-        <v>1.9802487517877101</v>
+        <v>1.9817528089107199</v>
       </c>
       <c r="D108" s="0">
-        <v>1.9748505762843533</v>
+        <v>1.9752038148451763</v>
       </c>
       <c r="E108" s="0">
-        <v>2.0772900779428003</v>
+        <v>2.077808144597324</v>
       </c>
       <c r="F108" s="0">
-        <v>1.8373267089607412</v>
+        <v>1.8414793698906191</v>
       </c>
       <c r="G108" s="0">
-        <v>0.028332001894728967</v>
+        <v>0.028717536912515169</v>
       </c>
       <c r="H108" s="0">
-        <v>0.066952354928218077</v>
+        <v>0.066967942631346949</v>
       </c>
       <c r="I108" s="0">
-        <v>0.1430175347321076</v>
+        <v>0.14030273186045777</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>2.0174863779752998</v>
+        <v>2.0176272127994799</v>
       </c>
       <c r="B109" s="0">
-        <v>2.1788129201179398</v>
+        <v>2.1763705048892299</v>
       </c>
       <c r="C109" s="0">
-        <v>2.00147523176246</v>
+        <v>2.0028115735982799</v>
       </c>
       <c r="D109" s="0">
-        <v>1.9819669546054117</v>
+        <v>1.9824546125548292</v>
       </c>
       <c r="E109" s="0">
-        <v>2.0952537945006751</v>
+        <v>2.0955384155928161</v>
       </c>
       <c r="F109" s="0">
-        <v>1.843769645132278</v>
+        <v>1.8478018340975502</v>
       </c>
       <c r="G109" s="0">
-        <v>0.03583994569256041</v>
+        <v>0.035123554077722108</v>
       </c>
       <c r="H109" s="0">
-        <v>0.082256490334070953</v>
+        <v>0.080896241493032289</v>
       </c>
       <c r="I109" s="0">
-        <v>0.15676590845678237</v>
+        <v>0.15367964169686732</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>2.0329537193176801</v>
+        <v>2.03123837039265</v>
       </c>
       <c r="B110" s="0">
-        <v>2.2056888774150298</v>
+        <v>2.2064505126235598</v>
       </c>
       <c r="C110" s="0">
-        <v>2.0145652012284798</v>
+        <v>2.0126492096120598</v>
       </c>
       <c r="D110" s="0">
-        <v>1.9890128829315894</v>
+        <v>1.9893220429532412</v>
       </c>
       <c r="E110" s="0">
-        <v>2.1122406164318215</v>
+        <v>2.1127081249176807</v>
       </c>
       <c r="F110" s="0">
-        <v>1.8495612408672708</v>
+        <v>1.8534838764950141</v>
       </c>
       <c r="G110" s="0">
-        <v>0.043366093266580183</v>
+        <v>0.04228815683888773</v>
       </c>
       <c r="H110" s="0">
-        <v>0.095759463294773375</v>
+        <v>0.095264301508841895</v>
       </c>
       <c r="I110" s="0">
-        <v>0.165854202809715</v>
+        <v>0.16036198367190629</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>2.0485308540376299</v>
+        <v>2.04950283946547</v>
       </c>
       <c r="B111" s="0">
-        <v>2.2448607829557301</v>
+        <v>2.2448753585652002</v>
       </c>
       <c r="C111" s="0">
-        <v>2.0390171407005799</v>
+        <v>2.03765361138294</v>
       </c>
       <c r="D111" s="0">
-        <v>1.9948570573044275</v>
+        <v>1.9953141992511247</v>
       </c>
       <c r="E111" s="0">
-        <v>2.1293392957214676</v>
+        <v>2.1297652756789813</v>
       </c>
       <c r="F111" s="0">
-        <v>1.8553589000639479</v>
+        <v>1.8591795064169769</v>
       </c>
       <c r="G111" s="0">
-        <v>0.053830102577417438</v>
+        <v>0.05348115932750442</v>
       </c>
       <c r="H111" s="0">
-        <v>0.11305416318446353</v>
+        <v>0.11307439999997278</v>
       </c>
       <c r="I111" s="0">
-        <v>0.18424646696348101</v>
+        <v>0.17922950941763666</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>2.06397838642483</v>
+        <v>2.0645731228867801</v>
       </c>
       <c r="B112" s="0">
-        <v>2.2700694295235802</v>
+        <v>2.2716166672270899</v>
       </c>
       <c r="C112" s="0">
-        <v>2.0666767663475198</v>
+        <v>2.06839089478177</v>
       </c>
       <c r="D112" s="0">
-        <v>2.0006190117888711</v>
+        <v>2.000943207692274</v>
       </c>
       <c r="E112" s="0">
-        <v>2.1450726604147823</v>
+        <v>2.1455931131924606</v>
       </c>
       <c r="F112" s="0">
-        <v>1.8607282991872038</v>
+        <v>1.8645490055313911</v>
       </c>
       <c r="G112" s="0">
-        <v>0.06279689447507894</v>
+        <v>0.063136772222631712</v>
       </c>
       <c r="H112" s="0">
-        <v>0.12621027601619395</v>
+        <v>0.12692785336369625</v>
       </c>
       <c r="I112" s="0">
-        <v>0.20421999492894655</v>
+        <v>0.20231921868256802</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>2.0756544755243902</v>
+        <v>2.0758255660169902</v>
       </c>
       <c r="B113" s="0">
-        <v>2.2993791045270902</v>
+        <v>2.3006523942749202</v>
       </c>
       <c r="C113" s="0">
-        <v>2.0762840139674399</v>
+        <v>2.0810740010294402</v>
       </c>
       <c r="D113" s="0">
-        <v>2.0055977837372145</v>
+        <v>2.0058251879777034</v>
       </c>
       <c r="E113" s="0">
-        <v>2.1603898841881004</v>
+        <v>2.1608590065620037</v>
       </c>
       <c r="F113" s="0">
-        <v>1.8653986395459714</v>
+        <v>1.8692166379093424</v>
       </c>
       <c r="G113" s="0">
-        <v>0.070721387084291834</v>
+        <v>0.070889012379073302</v>
       </c>
       <c r="H113" s="0">
-        <v>0.13896325416288707</v>
+        <v>0.13921584726204705</v>
       </c>
       <c r="I113" s="0">
-        <v>0.2126416686578454</v>
+        <v>0.21238219293937702</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>2.09114876115604</v>
+        <v>2.0894570669525101</v>
       </c>
       <c r="B114" s="0">
-        <v>2.3270595278194501</v>
+        <v>2.32443900421229</v>
       </c>
       <c r="C114" s="0">
-        <v>2.0979719173981799</v>
+        <v>2.0930328757174199</v>
       </c>
       <c r="D114" s="0">
-        <v>2.0099514719509952</v>
+        <v>2.010358689321234</v>
       </c>
       <c r="E114" s="0">
-        <v>2.1751142062408828</v>
+        <v>2.1752976656984311</v>
       </c>
       <c r="F114" s="0">
-        <v>1.8699985368910985</v>
+        <v>1.8734886319390869</v>
       </c>
       <c r="G114" s="0">
-        <v>0.080056825370605267</v>
+        <v>0.078654747350479934</v>
       </c>
       <c r="H114" s="0">
-        <v>0.15178157337204437</v>
+        <v>0.14998379576256979</v>
       </c>
       <c r="I114" s="0">
-        <v>0.22693811012098605</v>
+        <v>0.21963604539241147</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>2.1014843239137599</v>
+        <v>2.1023272285119301</v>
       </c>
       <c r="B115" s="0">
-        <v>2.3508163602800498</v>
+        <v>2.35050430892358</v>
       </c>
       <c r="C115" s="0">
-        <v>2.1043507308760399</v>
+        <v>2.1025045447825099</v>
       </c>
       <c r="D115" s="0">
-        <v>2.0136038500961484</v>
+        <v>2.0140323315661686</v>
       </c>
       <c r="E115" s="0">
-        <v>2.1890972700456417</v>
+        <v>2.1893807845484488</v>
       </c>
       <c r="F115" s="0">
-        <v>1.8739530113659397</v>
+        <v>1.8774248522901873</v>
       </c>
       <c r="G115" s="0">
-        <v>0.087146773961851776</v>
+        <v>0.086551076385170136</v>
       </c>
       <c r="H115" s="0">
-        <v>0.1612976285643978</v>
+        <v>0.16064395608544388</v>
       </c>
       <c r="I115" s="0">
-        <v>0.2303436744127757</v>
+        <v>0.22496243495473772</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>2.1079933775505801</v>
+        <v>2.10866790156259</v>
       </c>
       <c r="B116" s="0">
-        <v>2.3695804716987898</v>
+        <v>2.3711012400798301</v>
       </c>
       <c r="C116" s="0">
-        <v>2.1044751251396998</v>
+        <v>2.1063566649940202</v>
       </c>
       <c r="D116" s="0">
-        <v>2.0166025471197733</v>
+        <v>2.0168827827657076</v>
       </c>
       <c r="E116" s="0">
-        <v>2.2023366075308846</v>
+        <v>2.2027832453495617</v>
       </c>
       <c r="F116" s="0">
-        <v>1.8774436525560718</v>
+        <v>1.8809307461115625</v>
       </c>
       <c r="G116" s="0">
-        <v>0.09160794157102041</v>
+        <v>0.091951382428106437</v>
       </c>
       <c r="H116" s="0">
-        <v>0.16765671317471764</v>
+        <v>0.16836838965488216</v>
       </c>
       <c r="I116" s="0">
-        <v>0.22737629049401309</v>
+        <v>0.22559463761486256</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>2.1166169487544999</v>
+        <v>2.1168101834470701</v>
       </c>
       <c r="B117" s="0">
-        <v>2.3883640167474498</v>
+        <v>2.3897843711137599</v>
       </c>
       <c r="C117" s="0">
-        <v>2.1054034550427101</v>
+        <v>2.1076459902773901</v>
       </c>
       <c r="D117" s="0">
-        <v>2.0189734450309014</v>
+        <v>2.0191599264416782</v>
       </c>
       <c r="E117" s="0">
-        <v>2.2151573456036391</v>
+        <v>2.2155707772915103</v>
       </c>
       <c r="F117" s="0">
-        <v>1.8806333933383923</v>
+        <v>1.8840508382445977</v>
       </c>
       <c r="G117" s="0">
-        <v>0.095471573909728991</v>
+        <v>0.095671373939904922</v>
       </c>
       <c r="H117" s="0">
-        <v>0.17387498805143858</v>
+        <v>0.17422284716116812</v>
       </c>
       <c r="I117" s="0">
-        <v>0.22481959883992225</v>
+        <v>0.22328687021962873</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>2.1194148431986801</v>
+        <v>2.1177373673148701</v>
       </c>
       <c r="B118" s="0">
-        <v>2.40767467243337</v>
+        <v>2.40515565105762</v>
       </c>
       <c r="C118" s="0">
-        <v>2.1046715424034601</v>
+        <v>2.1025280896087599</v>
       </c>
       <c r="D118" s="0">
-        <v>2.0202607892585212</v>
+        <v>2.0205551948557097</v>
       </c>
       <c r="E118" s="0">
-        <v>2.2277605723852574</v>
+        <v>2.2278947462812706</v>
       </c>
       <c r="F118" s="0">
-        <v>1.8835777265902238</v>
+        <v>1.8867843116252931</v>
       </c>
       <c r="G118" s="0">
-        <v>0.098114220849379263</v>
+        <v>0.09701556003952154</v>
       </c>
       <c r="H118" s="0">
-        <v>0.17991479136741648</v>
+        <v>0.1783791566474506</v>
       </c>
       <c r="I118" s="0">
-        <v>0.22120100191505956</v>
+        <v>0.21611876788840151</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>2.1196145649488698</v>
+        <v>2.1203626993695002</v>
       </c>
       <c r="B119" s="0">
-        <v>2.4221770125058799</v>
+        <v>2.4218330486602602</v>
       </c>
       <c r="C119" s="0">
-        <v>2.0999143778884499</v>
+        <v>2.0979211026692601</v>
       </c>
       <c r="D119" s="0">
-        <v>2.0208336440502035</v>
+        <v>2.0211687879995646</v>
       </c>
       <c r="E119" s="0">
-        <v>2.2397655454886674</v>
+        <v>2.2399640531943321</v>
       </c>
       <c r="F119" s="0">
-        <v>1.8862159751639058</v>
+        <v>1.8893322334373459</v>
       </c>
       <c r="G119" s="0">
-        <v>0.09907570867299631</v>
+        <v>0.098726210030827086</v>
       </c>
       <c r="H119" s="0">
-        <v>0.18317731307975102</v>
+        <v>0.18246968481840228</v>
       </c>
       <c r="I119" s="0">
-        <v>0.21378304219078528</v>
+        <v>0.20901149394558555</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>2.12010570634274</v>
+        <v>2.1208370769436198</v>
       </c>
       <c r="B120" s="0">
-        <v>2.4328182187357799</v>
+        <v>2.4341236064885199</v>
       </c>
       <c r="C120" s="0">
-        <v>2.0875151286181799</v>
+        <v>2.08939434649337</v>
       </c>
       <c r="D120" s="0">
-        <v>2.0207894901650127</v>
+        <v>2.0210238184892337</v>
       </c>
       <c r="E120" s="0">
-        <v>2.251029902455616</v>
+        <v>2.251321280736799</v>
       </c>
       <c r="F120" s="0">
-        <v>1.8885438793839415</v>
+        <v>1.8916677124394097</v>
       </c>
       <c r="G120" s="0">
-        <v>0.096573680975607423</v>
+        <v>0.097034484546796404</v>
       </c>
       <c r="H120" s="0">
-        <v>0.18099414100806344</v>
+        <v>0.18108219733623365</v>
       </c>
       <c r="I120" s="0">
-        <v>0.19883081347370446</v>
+        <v>0.1973027055721468</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>2.1031255230733699</v>
+        <v>2.10334064989999</v>
       </c>
       <c r="B121" s="0">
-        <v>2.43021189335564</v>
+        <v>2.4281213702998401</v>
       </c>
       <c r="C121" s="0">
-        <v>2.06100720424041</v>
+        <v>2.0625894206578099</v>
       </c>
       <c r="D121" s="0">
-        <v>2.0198845078795968</v>
+        <v>2.0202198070636492</v>
       </c>
       <c r="E121" s="0">
-        <v>2.2609397860805815</v>
+        <v>2.2610341891698815</v>
       </c>
       <c r="F121" s="0">
-        <v>1.8905046720903036</v>
+        <v>1.8934998013975575</v>
       </c>
       <c r="G121" s="0">
-        <v>0.082681594615831133</v>
+        <v>0.082197075030554706</v>
       </c>
       <c r="H121" s="0">
-        <v>0.16694741141666211</v>
+        <v>0.16603842665793889</v>
       </c>
       <c r="I121" s="0">
-        <v>0.16986470455158975</v>
+        <v>0.16816392361393254</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>2.0735935900077802</v>
+        <v>2.0719204219021901</v>
       </c>
       <c r="B122" s="0">
-        <v>2.4087359912065902</v>
+        <v>2.40991543454866</v>
       </c>
       <c r="C122" s="0">
-        <v>2.0191538136314602</v>
+        <v>2.017820836581</v>
       </c>
       <c r="D122" s="0">
-        <v>2.0190508663008369</v>
+        <v>2.019177494390183</v>
       </c>
       <c r="E122" s="0">
-        <v>2.2689971905076596</v>
+        <v>2.2692712766510712</v>
       </c>
       <c r="F122" s="0">
-        <v>1.8919168271783131</v>
+        <v>1.8948041913161713</v>
       </c>
       <c r="G122" s="0">
-        <v>0.056488115785915276</v>
+        <v>0.055699536574950276</v>
       </c>
       <c r="H122" s="0">
-        <v>0.14225755238077378</v>
+        <v>0.14225418836893414</v>
       </c>
       <c r="I122" s="0">
-        <v>0.12751217808926463</v>
+        <v>0.12345897154233997</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>2.0493824404385901</v>
+        <v>2.0500617617274299</v>
       </c>
       <c r="B123" s="0">
-        <v>2.3987866680010401</v>
+        <v>2.39854869926251</v>
       </c>
       <c r="C123" s="0">
-        <v>1.9831138432575299</v>
+        <v>1.9808453066466101</v>
       </c>
       <c r="D123" s="0">
-        <v>2.0179102793173782</v>
+        <v>2.0182062340226614</v>
       </c>
       <c r="E123" s="0">
-        <v>2.2768342170112348</v>
+        <v>2.2769999186342558</v>
       </c>
       <c r="F123" s="0">
-        <v>1.8933888758613628</v>
+        <v>1.89612678160172</v>
       </c>
       <c r="G123" s="0">
-        <v>0.030790091975457588</v>
+        <v>0.030506476681788422</v>
       </c>
       <c r="H123" s="0">
-        <v>0.12204591345730015</v>
+        <v>0.12213090298480371</v>
       </c>
       <c r="I123" s="0">
-        <v>0.089874875862504686</v>
+        <v>0.085310713776936622</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>2.02681713098726</v>
+        <v>2.0275790272191201</v>
       </c>
       <c r="B124" s="0">
-        <v>2.3889655964498999</v>
+        <v>2.39009896577701</v>
       </c>
       <c r="C124" s="0">
-        <v>1.95608692109789</v>
+        <v>1.95822712801931</v>
       </c>
       <c r="D124" s="0">
-        <v>2.0166235842334745</v>
+        <v>2.0168103779689734</v>
       </c>
       <c r="E124" s="0">
-        <v>2.2840000065707766</v>
+        <v>2.2842222713882974</v>
       </c>
       <c r="F124" s="0">
-        <v>1.8949576633224423</v>
+        <v>1.8977074393370537</v>
       </c>
       <c r="G124" s="0">
-        <v>0.01000231847633325</v>
+        <v>0.010414715704882666</v>
       </c>
       <c r="H124" s="0">
-        <v>0.10501018002725612</v>
+        <v>0.10574578595050316</v>
       </c>
       <c r="I124" s="0">
-        <v>0.061603295909534193</v>
+        <v>0.060913870968246499</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>2.0110132622454602</v>
+        <v>2.0112697068581098</v>
       </c>
       <c r="B125" s="0">
-        <v>2.3797834897996601</v>
+        <v>2.3809904784820102</v>
       </c>
       <c r="C125" s="0">
-        <v>1.9414897040975001</v>
+        <v>1.94568424513397</v>
       </c>
       <c r="D125" s="0">
-        <v>2.0153197741931028</v>
+        <v>2.0153932972806219</v>
       </c>
       <c r="E125" s="0">
-        <v>2.2902287690143042</v>
+        <v>2.290418313948972</v>
       </c>
       <c r="F125" s="0">
-        <v>1.8967316431783383</v>
+        <v>1.8994483101348112</v>
       </c>
       <c r="G125" s="0">
-        <v>-0.0036710185271735234</v>
+        <v>-0.0034233754842715259</v>
       </c>
       <c r="H125" s="0">
-        <v>0.088693714004956584</v>
+        <v>0.089215862679527719</v>
       </c>
       <c r="I125" s="0">
-        <v>0.04491881843094199</v>
+        <v>0.045460595051486294</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>2.00006780519056</v>
+        <v>1.99838770695083</v>
       </c>
       <c r="B126" s="0">
-        <v>2.36521488810939</v>
+        <v>2.3631963692471398</v>
       </c>
       <c r="C126" s="0">
-        <v>1.9321344301878101</v>
+        <v>1.92815280772127</v>
       </c>
       <c r="D126" s="0">
-        <v>2.0144405022877883</v>
+        <v>2.0146035380745535</v>
       </c>
       <c r="E126" s="0">
-        <v>2.2950400025958122</v>
+        <v>2.2949963441838839</v>
       </c>
       <c r="F126" s="0">
-        <v>1.8985745090006092</v>
+        <v>1.9010030864560565</v>
       </c>
       <c r="G126" s="0">
-        <v>-0.011741021357577893</v>
+        <v>-0.012760873027464157</v>
       </c>
       <c r="H126" s="0">
-        <v>0.068833964746218251</v>
+        <v>0.067725404059263167</v>
       </c>
       <c r="I126" s="0">
-        <v>0.033187342320112896</v>
+        <v>0.027564673442893716</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>1.99615784506906</v>
+        <v>1.9967623102044401</v>
       </c>
       <c r="B127" s="0">
-        <v>2.3427122238386602</v>
+        <v>2.34265086261829</v>
       </c>
       <c r="C127" s="0">
-        <v>1.9189649965028901</v>
+        <v>1.91627663023512</v>
       </c>
       <c r="D127" s="0">
-        <v>2.0146384015681056</v>
+        <v>2.0148129066534231</v>
       </c>
       <c r="E127" s="0">
-        <v>2.2983020903055502</v>
+        <v>2.2983090626371605</v>
       </c>
       <c r="F127" s="0">
-        <v>1.9002922751785867</v>
+        <v>1.9026550954385117</v>
       </c>
       <c r="G127" s="0">
-        <v>-0.016469874967430975</v>
+        <v>-0.016589095416804995</v>
       </c>
       <c r="H127" s="0">
-        <v>0.044538482059469378</v>
+        <v>0.044155120689799439</v>
       </c>
       <c r="I127" s="0">
-        <v>0.018445278559199425</v>
+        <v>0.013722096672844719</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>1.9965248888435301</v>
+        <v>1.9973416393477099</v>
       </c>
       <c r="B128" s="0">
-        <v>2.3213293807276001</v>
+        <v>2.3221345360522001</v>
       </c>
       <c r="C128" s="0">
-        <v>1.90316755787664</v>
+        <v>1.9058004630627701</v>
       </c>
       <c r="D128" s="0">
-        <v>2.0156290429824955</v>
+        <v>2.0157466349938988</v>
       </c>
       <c r="E128" s="0">
-        <v>2.3009159550853568</v>
+        <v>2.3009359774061098</v>
       </c>
       <c r="F128" s="0">
-        <v>1.9020800860855878</v>
+        <v>1.904461310686256</v>
       </c>
       <c r="G128" s="0">
-        <v>-0.018589493966085981</v>
+        <v>-0.01799261008636897</v>
       </c>
       <c r="H128" s="0">
-        <v>0.021465865090427038</v>
+        <v>0.021503153628401578</v>
       </c>
       <c r="I128" s="0">
-        <v>0.00079279677966381931</v>
+        <v>0.00050340394034985791</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>1.99734563551925</v>
+        <v>1.99765013520447</v>
       </c>
       <c r="B129" s="0">
-        <v>2.3084636103129998</v>
+        <v>2.3057313277639802</v>
       </c>
       <c r="C129" s="0">
-        <v>1.8854808007647501</v>
+        <v>1.8868534755701201</v>
       </c>
       <c r="D129" s="0">
-        <v>2.0170610129001276</v>
+        <v>2.0173038052257093</v>
       </c>
       <c r="E129" s="0">
-        <v>2.303634271131632</v>
+        <v>2.3034463688013171</v>
       </c>
       <c r="F129" s="0">
-        <v>1.9040953347328793</v>
+        <v>1.9063136279710591</v>
       </c>
       <c r="G129" s="0">
-        <v>-0.017962999979697074</v>
+        <v>-0.018500675338611008</v>
       </c>
       <c r="H129" s="0">
-        <v>0.0047362332375552128</v>
+        <v>0.0038396511046135152</v>
       </c>
       <c r="I129" s="0">
-        <v>-0.018168438648966636</v>
+        <v>-0.019174064394733945</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>2.0064687321736501</v>
+        <v>2.0047124012909898</v>
       </c>
       <c r="B130" s="0">
-        <v>2.2993411647356199</v>
+        <v>2.3016843356539298</v>
       </c>
       <c r="C130" s="0">
-        <v>1.8716366170551999</v>
+        <v>1.8702603193985301</v>
       </c>
       <c r="D130" s="0">
-        <v>2.0193842673312306</v>
+        <v>2.0193078732548426</v>
       </c>
       <c r="E130" s="0">
-        <v>2.3062776826215781</v>
+        <v>2.3063922600491713</v>
       </c>
       <c r="F130" s="0">
-        <v>1.9064150882031228</v>
+        <v>1.9085480272405504</v>
       </c>
       <c r="G130" s="0">
-        <v>-0.014979026320660277</v>
+        <v>-0.015488988993639799</v>
       </c>
       <c r="H130" s="0">
-        <v>-0.0051804050372398032</v>
+        <v>-0.0044246852053496507</v>
       </c>
       <c r="I130" s="0">
-        <v>-0.034673409723222422</v>
+        <v>-0.038118728939696943</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>2.0101192164399699</v>
+        <v>2.0107272545275201</v>
       </c>
       <c r="B131" s="0">
-        <v>2.3019641579517001</v>
+        <v>2.30174360488494</v>
       </c>
       <c r="C131" s="0">
-        <v>1.8559061710967799</v>
+        <v>1.8526463777247</v>
       </c>
       <c r="D131" s="0">
-        <v>2.0214452848674576</v>
+        <v>2.0215811554425613</v>
       </c>
       <c r="E131" s="0">
-        <v>2.3093796682561654</v>
+        <v>2.3093041611217759</v>
       </c>
       <c r="F131" s="0">
-        <v>1.9091731024501837</v>
+        <v>1.9111180101991341</v>
       </c>
       <c r="G131" s="0">
-        <v>-0.012348590821482451</v>
+        <v>-0.012363301772072063</v>
       </c>
       <c r="H131" s="0">
-        <v>-0.0084096041873423059</v>
+        <v>-0.0080441945758171016</v>
       </c>
       <c r="I131" s="0">
-        <v>-0.0545444081040087</v>
+        <v>-0.058965417557140035</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>2.0095679643792499</v>
+        <v>2.01042095874495</v>
       </c>
       <c r="B132" s="0">
-        <v>2.29908872232141</v>
+        <v>2.2996084086326398</v>
       </c>
       <c r="C132" s="0">
-        <v>1.8233969273811199</v>
+        <v>1.82694324660861</v>
       </c>
       <c r="D132" s="0">
-        <v>2.0240749932572819</v>
+        <v>2.0241404261892129</v>
       </c>
       <c r="E132" s="0">
-        <v>2.3116779570791381</v>
+        <v>2.311578254091339</v>
       </c>
       <c r="F132" s="0">
-        <v>1.911845502650888</v>
+        <v>1.9138342866389988</v>
       </c>
       <c r="G132" s="0">
-        <v>-0.013788255467543087</v>
+        <v>-0.013228790341876668</v>
       </c>
       <c r="H132" s="0">
-        <v>-0.012996127299143907</v>
+        <v>-0.012376110970111619</v>
       </c>
       <c r="I132" s="0">
-        <v>-0.087751821558009188</v>
+        <v>-0.086631998009202488</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>2.0090830495999001</v>
+        <v>2.0094337662550399</v>
       </c>
       <c r="B133" s="0">
-        <v>2.29538405877364</v>
+        <v>2.2958356864299398</v>
       </c>
       <c r="C133" s="0">
-        <v>1.79910404345754</v>
+        <v>1.80360328191844</v>
       </c>
       <c r="D133" s="0">
-        <v>2.0272702380166607</v>
+        <v>2.0272550674697389</v>
       </c>
       <c r="E133" s="0">
-        <v>2.3130564539104745</v>
+        <v>2.3129224583962422</v>
       </c>
       <c r="F133" s="0">
-        <v>1.9149100643967572</v>
+        <v>1.9168305091358502</v>
       </c>
       <c r="G133" s="0">
-        <v>-0.017499744604184818</v>
+        <v>-0.01732431142358852</v>
       </c>
       <c r="H133" s="0">
-        <v>-0.018629195078501751</v>
+        <v>-0.01806116894547458</v>
       </c>
       <c r="I133" s="0">
-        <v>-0.114924026676268</v>
+        <v>-0.11330560093938569</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>2.0076030206960001</v>
+        <v>2.0057101351390099</v>
       </c>
       <c r="B134" s="0">
-        <v>2.28760805847035</v>
+        <v>2.28721169384754</v>
       </c>
       <c r="C134" s="0">
-        <v>1.78986217383135</v>
+        <v>1.78485256826286</v>
       </c>
       <c r="D134" s="0">
-        <v>2.0311540587770951</v>
+        <v>2.0311140966961445</v>
       </c>
       <c r="E134" s="0">
-        <v>2.3133851717497289</v>
+        <v>2.3131729581430771</v>
       </c>
       <c r="F134" s="0">
-        <v>1.91843244132258</v>
+        <v>1.9200593690039927</v>
       </c>
       <c r="G134" s="0">
-        <v>-0.022744924961521952</v>
+        <v>-0.023525445589313271</v>
       </c>
       <c r="H134" s="0">
-        <v>-0.024436236499202096</v>
+        <v>-0.024637468891460099</v>
       </c>
       <c r="I134" s="0">
-        <v>-0.12924878366808507</v>
+        <v>-0.13495899705221628</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>2.0073109563877898</v>
+        <v>2.0080002929224401</v>
       </c>
       <c r="B135" s="0">
-        <v>2.2874948951405099</v>
+        <v>2.2871178901965199</v>
       </c>
       <c r="C135" s="0">
-        <v>1.78234763505335</v>
+        <v>1.77862641908948</v>
       </c>
       <c r="D135" s="0">
-        <v>2.0354331114193167</v>
+        <v>2.0355042372809429</v>
       </c>
       <c r="E135" s="0">
-        <v>2.3132838171828007</v>
+        <v>2.3129922848357483</v>
       </c>
       <c r="F135" s="0">
-        <v>1.922209147331001</v>
+        <v>1.9237362661835595</v>
       </c>
       <c r="G135" s="0">
-        <v>-0.026972970594268234</v>
+        <v>-0.027041984707497187</v>
       </c>
       <c r="H135" s="0">
-        <v>-0.026993421917362388</v>
+        <v>-0.027102875184619377</v>
       </c>
       <c r="I135" s="0">
-        <v>-0.13969246795862694</v>
+        <v>-0.1443709325266713</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>2.0088292070436702</v>
+        <v>2.0097369330982802</v>
       </c>
       <c r="B136" s="0">
-        <v>2.2830068888036301</v>
+        <v>2.2830400908415101</v>
       </c>
       <c r="C136" s="0">
-        <v>1.7799481407319799</v>
+        <v>1.78448552238671</v>
       </c>
       <c r="D136" s="0">
-        <v>2.0406050824410542</v>
+        <v>2.0406113231325342</v>
       </c>
       <c r="E136" s="0">
-        <v>2.3120893323640357</v>
+        <v>2.3117916448577338</v>
       </c>
       <c r="F136" s="0">
-        <v>1.9262185497368738</v>
+        <v>1.9278120342074105</v>
       </c>
       <c r="G136" s="0">
-        <v>-0.031190369259953329</v>
+        <v>-0.03063003993198285</v>
       </c>
       <c r="H136" s="0">
-        <v>-0.029942499883695142</v>
+        <v>-0.029444282739685104</v>
       </c>
       <c r="I136" s="0">
-        <v>-0.14588540920192802</v>
+        <v>-0.14370036873854272</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>2.0112534488109701</v>
+        <v>2.0115115098129199</v>
       </c>
       <c r="B137" s="0">
-        <v>2.2754049618885199</v>
+        <v>2.27597786580115</v>
       </c>
       <c r="C137" s="0">
-        <v>1.78321140909807</v>
+        <v>1.7868352132822101</v>
       </c>
       <c r="D137" s="0">
-        <v>2.046471673757797</v>
+        <v>2.0463727902023701</v>
       </c>
       <c r="E137" s="0">
-        <v>2.3101266595141334</v>
+        <v>2.3098457924351727</v>
       </c>
       <c r="F137" s="0">
-        <v>1.9305231482408127</v>
+        <v>1.9320075691783472</v>
       </c>
       <c r="G137" s="0">
-        <v>-0.035523580249838545</v>
+        <v>-0.035349088314572119</v>
       </c>
       <c r="H137" s="0">
-        <v>-0.031113875842952939</v>
+        <v>-0.030321402466314838</v>
       </c>
       <c r="I137" s="0">
-        <v>-0.14845739995684498</v>
+        <v>-0.14692990777981305</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>2.0174460897817199</v>
+        <v>2.0155201320827598</v>
       </c>
       <c r="B138" s="0">
-        <v>2.28659402360495</v>
+        <v>2.2867144986935002</v>
       </c>
       <c r="C138" s="0">
-        <v>1.7799033493657199</v>
+        <v>1.77512049475574</v>
       </c>
       <c r="D138" s="0">
-        <v>2.0520458277481559</v>
+        <v>2.0518691850654207</v>
       </c>
       <c r="E138" s="0">
-        <v>2.3086802395616361</v>
+        <v>2.3083557739906708</v>
       </c>
       <c r="F138" s="0">
-        <v>1.9350832901782846</v>
+        <v>1.936303806867129</v>
       </c>
       <c r="G138" s="0">
-        <v>-0.03528115576874697</v>
+        <v>-0.035771965568039188</v>
       </c>
       <c r="H138" s="0">
-        <v>-0.024752331773004514</v>
+        <v>-0.024517581554621883</v>
       </c>
       <c r="I138" s="0">
-        <v>-0.1548068721866995</v>
+        <v>-0.16006380221853767</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>2.0235133215969499</v>
+        <v>2.0243184051531999</v>
       </c>
       <c r="B139" s="0">
-        <v>2.2828998100300502</v>
+        <v>2.28217994060511</v>
       </c>
       <c r="C139" s="0">
-        <v>1.7811037035817401</v>
+        <v>1.7770554035998001</v>
       </c>
       <c r="D139" s="0">
-        <v>2.0583268847331428</v>
+        <v>2.0582985692334015</v>
       </c>
       <c r="E139" s="0">
-        <v>2.3058566778952048</v>
+        <v>2.3053851439153719</v>
       </c>
       <c r="F139" s="0">
-        <v>1.9398230137523571</v>
+        <v>1.9409180030368818</v>
       </c>
       <c r="G139" s="0">
-        <v>-0.034069578154601897</v>
+        <v>-0.033801785378116733</v>
       </c>
       <c r="H139" s="0">
-        <v>-0.022462314209265664</v>
+        <v>-0.022631960284515022</v>
       </c>
       <c r="I139" s="0">
-        <v>-0.15786989495676487</v>
+        <v>-0.16224048196901811</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>2.0344152781136899</v>
+        <v>2.0353515424653899</v>
       </c>
       <c r="B140" s="0">
-        <v>2.2810426475035701</v>
+        <v>2.2808536231076499</v>
       </c>
       <c r="C140" s="0">
-        <v>1.79566085689539</v>
+        <v>1.8010667895917301</v>
       </c>
       <c r="D140" s="0">
-        <v>2.0648141629197152</v>
+        <v>2.0647381598778476</v>
       </c>
       <c r="E140" s="0">
-        <v>2.302312211136019</v>
+        <v>2.3017889747106604</v>
       </c>
       <c r="F140" s="0">
-        <v>1.9449955232890166</v>
+        <v>1.9461729404838208</v>
       </c>
       <c r="G140" s="0">
-        <v>-0.030354170401783613</v>
+        <v>-0.029633983298610448</v>
       </c>
       <c r="H140" s="0">
-        <v>-0.021441448472408055</v>
+        <v>-0.021477207124343537</v>
       </c>
       <c r="I140" s="0">
-        <v>-0.1498734961173693</v>
+        <v>-0.14680799818791695</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>2.04411752693699</v>
+        <v>2.0442012363297599</v>
       </c>
       <c r="B141" s="0">
-        <v>2.2734541652663798</v>
+        <v>2.27069870600456</v>
       </c>
       <c r="C141" s="0">
-        <v>1.8093797616338601</v>
+        <v>1.81128433606626</v>
       </c>
       <c r="D141" s="0">
-        <v>2.0716077877319252</v>
+        <v>2.0716212980824666</v>
       </c>
       <c r="E141" s="0">
-        <v>2.2978699148178734</v>
+        <v>2.2972183845808294</v>
       </c>
       <c r="F141" s="0">
-        <v>1.9502317814783057</v>
+        <v>1.9511965013995138</v>
       </c>
       <c r="G141" s="0">
-        <v>-0.025743776331887853</v>
+        <v>-0.026292543686914246</v>
       </c>
       <c r="H141" s="0">
-        <v>-0.023904542918309936</v>
+        <v>-0.024265897625700684</v>
       </c>
       <c r="I141" s="0">
-        <v>-0.14140448021924873</v>
+        <v>-0.14064176900764297</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>2.0587507150895199</v>
+        <v>2.0569075266588102</v>
       </c>
       <c r="B142" s="0">
-        <v>2.2648682516112899</v>
+        <v>2.2686534847825</v>
       </c>
       <c r="C142" s="0">
-        <v>1.8220222664167101</v>
+        <v>1.8183488818015101</v>
       </c>
       <c r="D142" s="0">
-        <v>2.0788295870384013</v>
+        <v>2.07846360383295</v>
       </c>
       <c r="E142" s="0">
-        <v>2.2925768384234684</v>
+        <v>2.2923283924432294</v>
       </c>
       <c r="F142" s="0">
-        <v>1.9554780417380462</v>
+        <v>1.956304795612039</v>
       </c>
       <c r="G142" s="0">
-        <v>-0.020856046755064236</v>
+        <v>-0.020967494763000364</v>
       </c>
       <c r="H142" s="0">
-        <v>-0.030613531286532662</v>
+        <v>-0.028802043701160913</v>
       </c>
       <c r="I142" s="0">
-        <v>-0.13204357965536237</v>
+        <v>-0.13607304763578729</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>2.0649411191926301</v>
+        <v>2.0657855482346501</v>
       </c>
       <c r="B143" s="0">
-        <v>2.23932214466139</v>
+        <v>2.2384916492869098</v>
       </c>
       <c r="C143" s="0">
-        <v>1.84895908529714</v>
+        <v>1.8448403829737099</v>
       </c>
       <c r="D143" s="0">
-        <v>2.0864864342618294</v>
+        <v>2.0864219346889858</v>
       </c>
       <c r="E143" s="0">
-        <v>2.2859019444711808</v>
+        <v>2.2853206593307926</v>
       </c>
       <c r="F143" s="0">
-        <v>1.9609904966041565</v>
+        <v>1.9616215226576008</v>
       </c>
       <c r="G143" s="0">
-        <v>-0.021361763813243135</v>
+        <v>-0.021014912926414737</v>
       </c>
       <c r="H143" s="0">
-        <v>-0.044204043026526925</v>
+        <v>-0.043642557876677569</v>
       </c>
       <c r="I143" s="0">
-        <v>-0.11253610702344501</v>
+        <v>-0.11636346756821091</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>2.0702689847421301</v>
+        <v>2.0712285233902401</v>
       </c>
       <c r="B144" s="0">
-        <v>2.2270397411573</v>
+        <v>2.2265866348986099</v>
       </c>
       <c r="C144" s="0">
-        <v>1.87263254906609</v>
+        <v>1.87870637929456</v>
       </c>
       <c r="D144" s="0">
-        <v>2.093869024227661</v>
+        <v>2.0937367285763497</v>
       </c>
       <c r="E144" s="0">
-        <v>2.2796001950225477</v>
+        <v>2.2789608980428557</v>
       </c>
       <c r="F144" s="0">
-        <v>1.9666086853523006</v>
+        <v>1.967331013847188</v>
       </c>
       <c r="G144" s="0">
-        <v>-0.022173933058961308</v>
+        <v>-0.021505477591015756</v>
       </c>
       <c r="H144" s="0">
-        <v>-0.053072904493849937</v>
+        <v>-0.052372656360523184</v>
       </c>
       <c r="I144" s="0">
-        <v>-0.094743744296087964</v>
+        <v>-0.090391578376732201</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>2.0824708060179402</v>
+        <v>2.0824088626954098</v>
       </c>
       <c r="B145" s="0">
-        <v>2.2138143916836799</v>
+        <v>2.2151032378558302</v>
       </c>
       <c r="C145" s="0">
-        <v>1.8842893465692101</v>
+        <v>1.8889112282971801</v>
       </c>
       <c r="D145" s="0">
-        <v>2.1018414687365898</v>
+        <v>2.1015463694923859</v>
       </c>
       <c r="E145" s="0">
-        <v>2.2731280577590183</v>
+        <v>2.2725849314351523</v>
       </c>
       <c r="F145" s="0">
-        <v>1.9719825058522098</v>
+        <v>1.9725902794724448</v>
       </c>
       <c r="G145" s="0">
-        <v>-0.020747476031735854</v>
+        <v>-0.020420275901009304</v>
       </c>
       <c r="H145" s="0">
-        <v>-0.059166163140034991</v>
+        <v>-0.057785533702710536</v>
       </c>
       <c r="I145" s="0">
-        <v>-0.087554564380097691</v>
+        <v>-0.08439331229430698</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>2.0928797248057398</v>
+        <v>2.0911947568265599</v>
       </c>
       <c r="B146" s="0">
-        <v>2.2039483862915201</v>
+        <v>2.2040390935115002</v>
       </c>
       <c r="C146" s="0">
-        <v>1.8929177663483201</v>
+        <v>1.8859579957228401</v>
       </c>
       <c r="D146" s="0">
-        <v>2.1095910955389527</v>
+        <v>2.1093205080255628</v>
       </c>
       <c r="E146" s="0">
-        <v>2.2670146013670993</v>
+        <v>2.2663756061549933</v>
       </c>
       <c r="F146" s="0">
-        <v>1.9774235563570397</v>
+        <v>1.9776733718857569</v>
       </c>
       <c r="G146" s="0">
-        <v>-0.016630031832255358</v>
+        <v>-0.017065158253654084</v>
       </c>
       <c r="H146" s="0">
-        <v>-0.061896267516745436</v>
+        <v>-0.061440400448204459</v>
       </c>
       <c r="I146" s="0">
-        <v>-0.084140268255954664</v>
+        <v>-0.090075377340223611</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>2.10911366511273</v>
+        <v>2.10986195054176</v>
       </c>
       <c r="B147" s="0">
-        <v>2.20213654175121</v>
+        <v>2.2008805484976102</v>
       </c>
       <c r="C147" s="0">
-        <v>1.90334264735298</v>
+        <v>1.8994835511413799</v>
       </c>
       <c r="D147" s="0">
-        <v>2.1171103821264201</v>
+        <v>2.1170016078137333</v>
       </c>
       <c r="E147" s="0">
-        <v>2.2615324114843509</v>
+        <v>2.2607302963075622</v>
       </c>
       <c r="F147" s="0">
-        <v>1.9829871598238211</v>
+        <v>1.9831445022125544</v>
       </c>
       <c r="G147" s="0">
-        <v>-0.0086833392314067306</v>
+        <v>-0.0085648187161455613</v>
       </c>
       <c r="H147" s="0">
-        <v>-0.060684931727170432</v>
+        <v>-0.060718306069302265</v>
       </c>
       <c r="I147" s="0">
-        <v>-0.080028307554816158</v>
+        <v>-0.083514895443555698</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>2.1254647289021502</v>
+        <v>2.1265086210875199</v>
       </c>
       <c r="B148" s="0">
-        <v>2.19196987263286</v>
+        <v>2.1919323802650701</v>
       </c>
       <c r="C148" s="0">
-        <v>1.90782924528237</v>
+        <v>1.9141532256342899</v>
       </c>
       <c r="D148" s="0">
-        <v>2.124762225869834</v>
+        <v>2.1245467636048159</v>
       </c>
       <c r="E148" s="0">
-        <v>2.2559541189758265</v>
+        <v>2.2552151417240895</v>
       </c>
       <c r="F148" s="0">
-        <v>1.9883430190305418</v>
+        <v>1.988596071634926</v>
       </c>
       <c r="G148" s="0">
-        <v>-0.0029854530432080724</v>
+        <v>-0.0022092279364122188</v>
       </c>
       <c r="H148" s="0">
-        <v>-0.061757677424746006</v>
+        <v>-0.0607720708838657</v>
       </c>
       <c r="I148" s="0">
-        <v>-0.080262803291913667</v>
+        <v>-0.075399894901736819</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>2.1292584659102398</v>
+        <v>2.1291226013646098</v>
       </c>
       <c r="B149" s="0">
-        <v>2.1928699849953799</v>
+        <v>2.19450438138534</v>
       </c>
       <c r="C149" s="0">
-        <v>1.91486767978963</v>
+        <v>1.9174809318175301</v>
       </c>
       <c r="D149" s="0">
-        <v>2.1310922646928909</v>
+        <v>2.1307208862897258</v>
       </c>
       <c r="E149" s="0">
-        <v>2.2513039342310668</v>
+        <v>2.2506710734744777</v>
       </c>
       <c r="F149" s="0">
-        <v>1.9939312008857315</v>
+        <v>1.9940109941451873</v>
       </c>
       <c r="G149" s="0">
-        <v>-0.0014384466053544696</v>
+        <v>-0.00098116625603668481</v>
       </c>
       <c r="H149" s="0">
-        <v>-0.061883724053089353</v>
+        <v>-0.060330017125549515</v>
       </c>
       <c r="I149" s="0">
-        <v>-0.078754618155331205</v>
+        <v>-0.076455118203186193</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>2.1301200742144699</v>
+        <v>2.1284704239296901</v>
       </c>
       <c r="B150" s="0">
-        <v>2.1764587750697402</v>
+        <v>2.17570700645939</v>
       </c>
       <c r="C150" s="0">
-        <v>1.9226491450660901</v>
+        <v>1.9172172433942001</v>
       </c>
       <c r="D150" s="0">
-        <v>2.1380749400815104</v>
+        <v>2.13775061733807</v>
       </c>
       <c r="E150" s="0">
-        <v>2.2457925237256613</v>
+        <v>2.2450027220246485</v>
       </c>
       <c r="F150" s="0">
-        <v>1.9992714089714438</v>
+        <v>1.9990503621604188</v>
       </c>
       <c r="G150" s="0">
-        <v>-0.0066063467044897928</v>
+        <v>-0.0069655256485319315</v>
       </c>
       <c r="H150" s="0">
-        <v>-0.067435558786985567</v>
+        <v>-0.067170509542830353</v>
       </c>
       <c r="I150" s="0">
-        <v>-0.077002768777610919</v>
+        <v>-0.081426012930821565</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>2.1332806162567102</v>
+        <v>2.1339650579263698</v>
       </c>
       <c r="B151" s="0">
-        <v>2.17314940445296</v>
+        <v>2.1720057640513502</v>
       </c>
       <c r="C151" s="0">
-        <v>1.9298856978500101</v>
+        <v>1.9266945570243501</v>
       </c>
       <c r="D151" s="0">
-        <v>2.1449063118008405</v>
+        <v>2.1447103999508972</v>
       </c>
       <c r="E151" s="0">
-        <v>2.2410614093869263</v>
+        <v>2.2401745705531293</v>
       </c>
       <c r="F151" s="0">
-        <v>2.0045537517889622</v>
+        <v>2.0042231599829528</v>
       </c>
       <c r="G151" s="0">
-        <v>-0.012591183247378141</v>
+        <v>-0.012277661694652648</v>
       </c>
       <c r="H151" s="0">
-        <v>-0.06779864296915146</v>
+        <v>-0.067766414915187395</v>
       </c>
       <c r="I151" s="0">
-        <v>-0.074502936369473333</v>
+        <v>-0.076749006456494143</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>2.1320653506181699</v>
+        <v>2.1332190116678902</v>
       </c>
       <c r="B152" s="0">
-        <v>2.1770767886872702</v>
+        <v>2.1776303386654199</v>
       </c>
       <c r="C152" s="0">
-        <v>1.9399032373901399</v>
+        <v>1.9460067619242201</v>
       </c>
       <c r="D152" s="0">
-        <v>2.1515032948825628</v>
+        <v>2.1512157486792596</v>
       </c>
       <c r="E152" s="0">
-        <v>2.2369892617855163</v>
+        <v>2.236178668038892</v>
       </c>
       <c r="F152" s="0">
-        <v>2.0098714256454859</v>
+        <v>2.0096136667777529</v>
       </c>
       <c r="G152" s="0">
-        <v>-0.018210668367593129</v>
+        <v>-0.017150211619848872</v>
       </c>
       <c r="H152" s="0">
-        <v>-0.063142915067132127</v>
+        <v>-0.062312627154930765</v>
       </c>
       <c r="I152" s="0">
-        <v>-0.069754772962467182</v>
+        <v>-0.064708519928138614</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>2.1421984459497598</v>
+        <v>2.1420134263421899</v>
       </c>
       <c r="B153" s="0">
-        <v>2.16779683126969</v>
+        <v>2.16613692758835</v>
       </c>
       <c r="C153" s="0">
-        <v>1.9518593399539801</v>
+        <v>1.9524415301231499</v>
       </c>
       <c r="D153" s="0">
-        <v>2.1590618947528384</v>
+        <v>2.1588432653560816</v>
       </c>
       <c r="E153" s="0">
-        <v>2.2328866662662641</v>
+        <v>2.231987784134672</v>
       </c>
       <c r="F153" s="0">
-        <v>2.0149703576179236</v>
+        <v>2.0144444548542166</v>
       </c>
       <c r="G153" s="0">
-        <v>-0.022192891107684094</v>
+        <v>-0.022343669172040115</v>
       </c>
       <c r="H153" s="0">
-        <v>-0.053944047261677459</v>
+        <v>-0.05371502048220355</v>
       </c>
       <c r="I153" s="0">
-        <v>-0.064149408549736178</v>
+        <v>-0.062857000040237782</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>2.1501672889521402</v>
+        <v>2.1484674555482202</v>
       </c>
       <c r="B154" s="0">
-        <v>2.2177703042757</v>
+        <v>2.2194219550231602</v>
       </c>
       <c r="C154" s="0">
-        <v>1.9617305222317101</v>
+        <v>1.95809059391222</v>
       </c>
       <c r="D154" s="0">
-        <v>2.1633707337566768</v>
+        <v>2.1629600204119694</v>
       </c>
       <c r="E154" s="0">
-        <v>2.2327611569451506</v>
+        <v>2.2320825188673719</v>
       </c>
       <c r="F154" s="0">
-        <v>2.0207257505961222</v>
+        <v>2.0200273938645261</v>
       </c>
       <c r="G154" s="0">
-        <v>-0.012716288205054261</v>
+        <v>-0.013000768957506655</v>
       </c>
       <c r="H154" s="0">
-        <v>-0.025015399609384464</v>
+        <v>-0.023872359878939924</v>
       </c>
       <c r="I154" s="0">
-        <v>-0.057860625435520951</v>
+        <v>-0.060383283088304672</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>2.1619720010449499</v>
+        <v>2.1626510110249</v>
       </c>
       <c r="B155" s="0">
-        <v>2.21222536353836</v>
+        <v>2.2114018707292198</v>
       </c>
       <c r="C155" s="0">
-        <v>1.97373599277666</v>
+        <v>1.97130345328476</v>
       </c>
       <c r="D155" s="0">
-        <v>2.1696021846503704</v>
+        <v>2.169414597963327</v>
       </c>
       <c r="E155" s="0">
-        <v>2.2295671425448118</v>
+        <v>2.2287452168773876</v>
       </c>
       <c r="F155" s="0">
-        <v>2.0260216690491877</v>
+        <v>2.0251630159233125</v>
       </c>
       <c r="G155" s="0">
-        <v>-0.0058742891868437978</v>
+        <v>-0.0055946578216012309</v>
       </c>
       <c r="H155" s="0">
-        <v>-0.01706091047319535</v>
+        <v>-0.016204178751118722</v>
       </c>
       <c r="I155" s="0">
-        <v>-0.052011225245451424</v>
+        <v>-0.053021862824784743</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>2.1736215785069102</v>
+        <v>2.1749027471182401</v>
       </c>
       <c r="B156" s="0">
-        <v>2.20512872495974</v>
+        <v>2.2065130934072799</v>
       </c>
       <c r="C156" s="0">
-        <v>1.9893961442478001</v>
+        <v>1.99476646115749</v>
       </c>
       <c r="D156" s="0">
-        <v>2.1759450527112421</v>
+        <v>2.1756324978372414</v>
       </c>
       <c r="E156" s="0">
-        <v>2.2258424352971984</v>
+        <v>2.2251644556617691</v>
       </c>
       <c r="F156" s="0">
-        <v>2.0313202111934241</v>
+        <v>2.0305048429689956</v>
       </c>
       <c r="G156" s="0">
-        <v>-0.0041921541316518292</v>
+        <v>-0.0030095701090733793</v>
       </c>
       <c r="H156" s="0">
-        <v>-0.018545028444589228</v>
+        <v>-0.016687252846971892</v>
       </c>
       <c r="I156" s="0">
-        <v>-0.042680576142062727</v>
+        <v>-0.037400887427534883</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>2.1720914202686101</v>
+        <v>2.1718927323793298</v>
       </c>
       <c r="B157" s="0">
-        <v>2.2034407245818701</v>
+        <v>2.2049578522914</v>
       </c>
       <c r="C157" s="0">
-        <v>2.0006202531957298</v>
+        <v>2.0027636657564201</v>
       </c>
       <c r="D157" s="0">
-        <v>2.18159845077186</v>
+        <v>2.1811949592703597</v>
       </c>
       <c r="E157" s="0">
-        <v>2.2228796191888018</v>
+        <v>2.22222900775188</v>
       </c>
       <c r="F157" s="0">
-        <v>2.0366937640003062</v>
+        <v>2.0356897442517869</v>
       </c>
       <c r="G157" s="0">
-        <v>-0.0057078746232082783</v>
+        <v>-0.0051179131705209819</v>
       </c>
       <c r="H157" s="0">
-        <v>-0.019738804205664918</v>
+        <v>-0.018400240920154735</v>
       </c>
       <c r="I157" s="0">
-        <v>-0.035676256059909893</v>
+        <v>-0.032795269128915901</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>2.1831239796472199</v>
+        <v>2.1812585853662698</v>
       </c>
       <c r="B158" s="0">
-        <v>2.20060638587423</v>
+        <v>2.1978249382841302</v>
       </c>
       <c r="C158" s="0">
-        <v>2.0149639638039898</v>
+        <v>2.0099514997610202</v>
       </c>
       <c r="D158" s="0">
-        <v>2.1881525843038436</v>
+        <v>2.1879326888823876</v>
       </c>
       <c r="E158" s="0">
-        <v>2.2199254468302834</v>
+        <v>2.219036418047335</v>
       </c>
       <c r="F158" s="0">
-        <v>2.0420785195918176</v>
+        <v>2.0407470785116644</v>
       </c>
       <c r="G158" s="0">
-        <v>-0.0059576214404559093</v>
+        <v>-0.0068735255153439048</v>
       </c>
       <c r="H158" s="0">
-        <v>-0.020664677944564856</v>
+        <v>-0.021370115992054114</v>
       </c>
       <c r="I158" s="0">
-        <v>-0.027242763491250172</v>
+        <v>-0.030175059778470389</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>2.1872601034867398</v>
+        <v>2.18797193503441</v>
       </c>
       <c r="B159" s="0">
-        <v>2.1901972609952201</v>
+        <v>2.1902476233273398</v>
       </c>
       <c r="C159" s="0">
-        <v>2.0253195436887701</v>
+        <v>2.0234249659130898</v>
       </c>
       <c r="D159" s="0">
-        <v>2.1950022721202682</v>
+        <v>2.1948202431932402</v>
       </c>
       <c r="E159" s="0">
-        <v>2.217018784579003</v>
+        <v>2.2163086376486536</v>
       </c>
       <c r="F159" s="0">
-        <v>2.0474573568000936</v>
+        <v>2.0460490451450135</v>
       </c>
       <c r="G159" s="0">
-        <v>-0.0092432152052762343</v>
+        <v>-0.0091102130054276555</v>
       </c>
       <c r="H159" s="0">
-        <v>-0.023151216372548453</v>
+        <v>-0.022595227106253925</v>
       </c>
       <c r="I159" s="0">
-        <v>-0.022507382370146056</v>
+        <v>-0.02268739534686541</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>2.1900816150457598</v>
+        <v>2.19148440187158</v>
       </c>
       <c r="B160" s="0">
-        <v>2.1986259138220401</v>
+        <v>2.2003101603967998</v>
       </c>
       <c r="C160" s="0">
-        <v>2.0314859884639098</v>
+        <v>2.0360575346493599</v>
       </c>
       <c r="D160" s="0">
-        <v>2.2010276064736405</v>
+        <v>2.2007564601300742</v>
       </c>
       <c r="E160" s="0">
-        <v>2.2155607071091175</v>
+        <v>2.2150595649437173</v>
       </c>
       <c r="F160" s="0">
-        <v>2.053131582248275</v>
+        <v>2.0517307995242393</v>
       </c>
       <c r="G160" s="0">
-        <v>-0.011421975698888627</v>
+        <v>-0.010133669556818178</v>
       </c>
       <c r="H160" s="0">
-        <v>-0.019885792369231287</v>
+        <v>-0.018080436899993075</v>
       </c>
       <c r="I160" s="0">
-        <v>-0.021132254016093924</v>
+        <v>-0.016126962750262486</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>2.1911642749317002</v>
+        <v>2.1909832688330999</v>
       </c>
       <c r="B161" s="0">
-        <v>2.1918909486151099</v>
+        <v>2.1926546904237099</v>
       </c>
       <c r="C161" s="0">
-        <v>2.03651141277992</v>
+        <v>2.0363010813728399</v>
       </c>
       <c r="D161" s="0">
-        <v>2.2077122328773569</v>
+        <v>2.2074248894641393</v>
       </c>
       <c r="E161" s="0">
-        <v>2.2134648081951096</v>
+        <v>2.2129656994705584</v>
       </c>
       <c r="F161" s="0">
-        <v>2.0588404554171644</v>
+        <v>2.0571925191818146</v>
       </c>
       <c r="G161" s="0">
-        <v>-0.015616980926757404</v>
+        <v>-0.015202353347251755</v>
       </c>
       <c r="H161" s="0">
-        <v>-0.021767218741422078</v>
+        <v>-0.021049403556044406</v>
       </c>
       <c r="I161" s="0">
-        <v>-0.022954112510650885</v>
+        <v>-0.021137502803992292</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>2.1970215181497799</v>
+        <v>2.1950364799540698</v>
       </c>
       <c r="B162" s="0">
-        <v>2.1844646388181101</v>
+        <v>2.1816231958780099</v>
       </c>
       <c r="C162" s="0">
-        <v>2.0344762855167899</v>
+        <v>2.0321905622027199</v>
       </c>
       <c r="D162" s="0">
-        <v>2.2149155042855648</v>
+        <v>2.2147523603699946</v>
       </c>
       <c r="E162" s="0">
-        <v>2.2113454385451865</v>
+        <v>2.2107090074413276</v>
       </c>
       <c r="F162" s="0">
-        <v>2.0645206591132679</v>
+        <v>2.062653136833231</v>
       </c>
       <c r="G162" s="0">
-        <v>-0.019193691405768227</v>
+        <v>-0.020184716825289047</v>
       </c>
       <c r="H162" s="0">
-        <v>-0.024833104196516485</v>
+        <v>-0.025752042020871814</v>
       </c>
       <c r="I162" s="0">
-        <v>-0.029292365481627669</v>
+        <v>-0.0297216509062922</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>2.2041605543516201</v>
+        <v>2.2048755135129299</v>
       </c>
       <c r="B163" s="0">
-        <v>2.1860423499135102</v>
+        <v>2.18671285413068</v>
       </c>
       <c r="C163" s="0">
-        <v>2.0409875219328799</v>
+        <v>2.03946457733133</v>
       </c>
       <c r="D163" s="0">
-        <v>2.2216818569202488</v>
+        <v>2.2215702824634485</v>
       </c>
       <c r="E163" s="0">
-        <v>2.2101374507355187</v>
+        <v>2.209770061464833</v>
       </c>
       <c r="F163" s="0">
-        <v>2.0707383449956134</v>
+        <v>2.0687337625420361</v>
       </c>
       <c r="G163" s="0">
-        <v>-0.016976770585579216</v>
+        <v>-0.01685396371681807</v>
       </c>
       <c r="H163" s="0">
-        <v>-0.023994478777059281</v>
+        <v>-0.023409985756241623</v>
       </c>
       <c r="I163" s="0">
-        <v>-0.030177141113825801</v>
+        <v>-0.029204093344271372</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>2.21665894397107</v>
+        <v>2.2180657482252299</v>
       </c>
       <c r="B164" s="0">
-        <v>2.1832225705889301</v>
+        <v>2.18501412455175</v>
       </c>
       <c r="C164" s="0">
-        <v>2.0428875363427901</v>
+        <v>2.0465654491447598</v>
       </c>
       <c r="D164" s="0">
-        <v>2.2288769917361861</v>
+        <v>2.2287300386176039</v>
       </c>
       <c r="E164" s="0">
-        <v>2.208856271217698</v>
+        <v>2.2087041565487922</v>
       </c>
       <c r="F164" s="0">
-        <v>2.0770587289509637</v>
+        <v>2.0750195063757588</v>
       </c>
       <c r="G164" s="0">
-        <v>-0.010211256161231374</v>
+        <v>-0.0089700758954517328</v>
       </c>
       <c r="H164" s="0">
-        <v>-0.026977698617558929</v>
+        <v>-0.025560863953418986</v>
       </c>
       <c r="I164" s="0">
-        <v>-0.034199551972168153</v>
+        <v>-0.028931110088491797</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>2.2281639385080698</v>
+        <v>2.22813495625094</v>
       </c>
       <c r="B165" s="0">
-        <v>2.1688956745080099</v>
+        <v>2.1688193621763698</v>
       </c>
       <c r="C165" s="0">
-        <v>2.0418372337716302</v>
+        <v>2.0441496955849598</v>
       </c>
       <c r="D165" s="0">
-        <v>2.2369941416303156</v>
+        <v>2.2368805083073706</v>
       </c>
       <c r="E165" s="0">
-        <v>2.2066410540864507</v>
+        <v>2.2064860202865435</v>
       </c>
       <c r="F165" s="0">
-        <v>2.0834125685139782</v>
+        <v>2.0811848901225916</v>
       </c>
       <c r="G165" s="0">
-        <v>-0.0073321321809787926</v>
+        <v>-0.0071072684871048546</v>
       </c>
       <c r="H165" s="0">
-        <v>-0.042037548440487404</v>
+        <v>-0.042031863887683922</v>
       </c>
       <c r="I165" s="0">
-        <v>-0.04073695737532608</v>
+        <v>-0.036699196494353187</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>2.2308724614953199</v>
+        <v>2.2287768204568201</v>
       </c>
       <c r="B166" s="0">
-        <v>2.1276114312761498</v>
+        <v>2.1248275671603798</v>
       </c>
       <c r="C166" s="0">
-        <v>2.0450852680379801</v>
+        <v>2.0408255955721999</v>
       </c>
       <c r="D166" s="0">
-        <v>2.2465549474642574</v>
+        <v>2.2465766526250741</v>
       </c>
       <c r="E166" s="0">
-        <v>2.2030703308585315</v>
+        <v>2.2029056823618154</v>
       </c>
       <c r="F166" s="0">
-        <v>2.0898303049411036</v>
+        <v>2.0872859131339463</v>
       </c>
       <c r="G166" s="0">
-        <v>-0.019016136155744368</v>
+        <v>-0.020384952746041185</v>
       </c>
       <c r="H166" s="0">
-        <v>-0.068638711562281768</v>
+        <v>-0.070033029196552563</v>
       </c>
       <c r="I166" s="0">
-        <v>-0.046000359741127358</v>
+        <v>-0.046985676258813433</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>2.2167370005576399</v>
+        <v>2.21735159416968</v>
       </c>
       <c r="B167" s="0">
-        <v>2.1225431903980301</v>
+        <v>2.1242413171834</v>
       </c>
       <c r="C167" s="0">
-        <v>2.04089681835005</v>
+        <v>2.0395617877620098</v>
       </c>
       <c r="D167" s="0">
-        <v>2.2546388116660254</v>
+        <v>2.2546460885865764</v>
       </c>
       <c r="E167" s="0">
-        <v>2.201944114765594</v>
+        <v>2.2021999925422087</v>
       </c>
       <c r="F167" s="0">
-        <v>2.0967704310660764</v>
+        <v>2.0941497509562983</v>
       </c>
       <c r="G167" s="0">
-        <v>-0.037047175085481832</v>
+        <v>-0.036918988629640728</v>
       </c>
       <c r="H167" s="0">
-        <v>-0.082542981922212266</v>
+        <v>-0.082015145968293846</v>
       </c>
       <c r="I167" s="0">
-        <v>-0.055767949896967609</v>
+        <v>-0.054333083033759701</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>2.2082478126272802</v>
+        <v>2.2097349905311501</v>
       </c>
       <c r="B168" s="0">
-        <v>2.1064140790722798</v>
+        <v>2.1077146286165398</v>
       </c>
       <c r="C168" s="0">
-        <v>2.0365569676573698</v>
+        <v>2.0394529175001801</v>
       </c>
       <c r="D168" s="0">
-        <v>2.2640611437921927</v>
+        <v>2.2641351912730507</v>
       </c>
       <c r="E168" s="0">
-        <v>2.2004009934524809</v>
+        <v>2.2008380095481099</v>
       </c>
       <c r="F168" s="0">
-        <v>2.1037929170969774</v>
+        <v>2.101088899613393</v>
       </c>
       <c r="G168" s="0">
-        <v>-0.055915807169291266</v>
+        <v>-0.054863649129865834</v>
       </c>
       <c r="H168" s="0">
-        <v>-0.092395131351380833</v>
+        <v>-0.091794285549065047</v>
       </c>
       <c r="I168" s="0">
-        <v>-0.066898151727895816</v>
+        <v>-0.061798324169992778</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>2.2051379729156002</v>
+        <v>2.20517662530029</v>
       </c>
       <c r="B169" s="0">
-        <v>2.1079166562584302</v>
+        <v>2.1071410999720599</v>
       </c>
       <c r="C169" s="0">
-        <v>2.0412941115101302</v>
+        <v>2.0421165197000999</v>
       </c>
       <c r="D169" s="0">
-        <v>2.2736145063465591</v>
+        <v>2.2737683372726107</v>
       </c>
       <c r="E169" s="0">
-        <v>2.199559870452755</v>
+        <v>2.2000470127351699</v>
       </c>
       <c r="F169" s="0">
-        <v>2.1113445213489359</v>
+        <v>2.1084151963351405</v>
       </c>
       <c r="G169" s="0">
-        <v>-0.066144489323855624</v>
+        <v>-0.066348360533881795</v>
       </c>
       <c r="H169" s="0">
-        <v>-0.092960374963678719</v>
+        <v>-0.094066001387602169</v>
       </c>
       <c r="I169" s="0">
-        <v>-0.069710824633202675</v>
+        <v>-0.066020790054023726</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>2.2153393865548798</v>
+        <v>2.2132593272384602</v>
       </c>
       <c r="B170" s="0">
-        <v>2.1089387698228901</v>
+        <v>2.10658593510166</v>
       </c>
       <c r="C170" s="0">
-        <v>2.0550581173368099</v>
+        <v>2.05292877156944</v>
       </c>
       <c r="D170" s="0">
-        <v>2.2843834373990308</v>
+        <v>2.2845901111859188</v>
       </c>
       <c r="E170" s="0">
-        <v>2.1983887453193289</v>
+        <v>2.1990464055620667</v>
       </c>
       <c r="F170" s="0">
-        <v>2.1191749762676757</v>
+        <v>2.1160133106572809</v>
       </c>
       <c r="G170" s="0">
-        <v>-0.064993313821996163</v>
+        <v>-0.066461729848530118</v>
       </c>
       <c r="H170" s="0">
-        <v>-0.090296912152246417</v>
+        <v>-0.092168432417713442</v>
       </c>
       <c r="I170" s="0">
-        <v>-0.064567719297807441</v>
+        <v>-0.063346199539081591</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>2.2411501893065102</v>
+        <v>2.2416279691399601</v>
       </c>
       <c r="B171" s="0">
-        <v>2.11066688691615</v>
+        <v>2.1131051480318002</v>
       </c>
       <c r="C171" s="0">
-        <v>2.0706308463883101</v>
+        <v>2.0692826534340201</v>
       </c>
       <c r="D171" s="0">
-        <v>2.2966636925201365</v>
+        <v>2.2968517274040257</v>
       </c>
       <c r="E171" s="0">
-        <v>2.1969154344925137</v>
+        <v>2.1980945797399234</v>
       </c>
       <c r="F171" s="0">
-        <v>2.1270640577978388</v>
+        <v>2.1237778584084275</v>
       </c>
       <c r="G171" s="0">
-        <v>-0.055397691172095302</v>
+        <v>-0.055179407942184323</v>
       </c>
       <c r="H171" s="0">
-        <v>-0.086689651563062686</v>
+        <v>-0.086773593518714831</v>
       </c>
       <c r="I171" s="0">
-        <v>-0.056181997106953006</v>
+        <v>-0.05385870579746839</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>2.2675192035328999</v>
+        <v>2.2690342614505301</v>
       </c>
       <c r="B172" s="0">
-        <v>2.1141613166759101</v>
+        <v>2.1147552138251302</v>
       </c>
       <c r="C172" s="0">
-        <v>2.0933714195239101</v>
+        <v>2.09559312338784</v>
       </c>
       <c r="D172" s="0">
-        <v>2.3095415100358805</v>
+        <v>2.3099299288934754</v>
       </c>
       <c r="E172" s="0">
-        <v>2.1958368619926532</v>
+        <v>2.1971341778027242</v>
       </c>
       <c r="F172" s="0">
-        <v>2.1352871555389088</v>
+        <v>2.1318724401277995</v>
       </c>
       <c r="G172" s="0">
-        <v>-0.044103612026297978</v>
+        <v>-0.043296751930609625</v>
       </c>
       <c r="H172" s="0">
-        <v>-0.079737753145030038</v>
+        <v>-0.08100550449383756</v>
       </c>
       <c r="I172" s="0">
-        <v>-0.041758075184313764</v>
+        <v>-0.036658262287391413</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>2.29227423820904</v>
+        <v>2.2924083585602402</v>
       </c>
       <c r="B173" s="0">
-        <v>2.1315784037465701</v>
+        <v>2.1269128412863201</v>
       </c>
       <c r="C173" s="0">
-        <v>2.12095545261031</v>
+        <v>2.1208201222947598</v>
       </c>
       <c r="D173" s="0">
-        <v>2.3220807778492238</v>
+        <v>2.3227774798024843</v>
       </c>
       <c r="E173" s="0">
-        <v>2.1962132152425275</v>
+        <v>2.197493647558074</v>
       </c>
       <c r="F173" s="0">
-        <v>2.1440013084714904</v>
+        <v>2.1402994315066195</v>
       </c>
       <c r="G173" s="0">
-        <v>-0.031006936935088235</v>
+        <v>-0.032360665873157085</v>
       </c>
       <c r="H173" s="0">
-        <v>-0.062438852142346707</v>
+        <v>-0.066189304395658927</v>
       </c>
       <c r="I173" s="0">
-        <v>-0.024160020690796726</v>
+        <v>-0.020517841366091076</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>2.31890202097</v>
+        <v>2.31682811463839</v>
       </c>
       <c r="B174" s="0">
-        <v>2.1625140414737398</v>
+        <v>2.1641330900193898</v>
       </c>
       <c r="C174" s="0">
-        <v>2.1383201530687899</v>
+        <v>2.13778739102115</v>
       </c>
       <c r="D174" s="0">
-        <v>2.3343983519308349</v>
+        <v>2.334813585498988</v>
       </c>
       <c r="E174" s="0">
-        <v>2.1977236936119193</v>
+        <v>2.1997927394173398</v>
       </c>
       <c r="F174" s="0">
-        <v>2.1528629000690565</v>
+        <v>2.1490566663399853</v>
       </c>
       <c r="G174" s="0">
-        <v>-0.013072926589632144</v>
+        <v>-0.0145924770301466</v>
       </c>
       <c r="H174" s="0">
-        <v>-0.037431916379574701</v>
+        <v>-0.0388697320399519</v>
       </c>
       <c r="I174" s="0">
-        <v>-0.013342342012388667</v>
+        <v>-0.01013079245441754</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>2.3582375438162102</v>
+        <v>2.35856188830491</v>
       </c>
       <c r="B175" s="0">
-        <v>2.18083663422179</v>
+        <v>2.1837711689240602</v>
       </c>
       <c r="C175" s="0">
-        <v>2.1620668083234098</v>
+        <v>2.16051674542702</v>
       </c>
       <c r="D175" s="0">
-        <v>2.3476880530315847</v>
+        <v>2.3482309224864699</v>
       </c>
       <c r="E175" s="0">
-        <v>2.198380671979093</v>
+        <v>2.2009127677199807</v>
       </c>
       <c r="F175" s="0">
-        <v>2.1618993463117717</v>
+        <v>2.1578907871492254</v>
       </c>
       <c r="G175" s="0">
-        <v>0.006107986743754317</v>
+        <v>0.0060511752228337452</v>
       </c>
       <c r="H175" s="0">
-        <v>-0.017897610685617377</v>
+        <v>-0.018372849557265012</v>
       </c>
       <c r="I175" s="0">
-        <v>-8.2513821966870044e-05</v>
+        <v>0.0028880334250116439</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>2.3743773905718202</v>
+        <v>2.3759730470973701</v>
       </c>
       <c r="B176" s="0">
-        <v>2.1915818094874902</v>
+        <v>2.1915053142907701</v>
       </c>
       <c r="C176" s="0">
-        <v>2.1784654253371101</v>
+        <v>2.18038056520904</v>
       </c>
       <c r="D176" s="0">
-        <v>2.3602128268855078</v>
+        <v>2.3610285991123066</v>
       </c>
       <c r="E176" s="0">
-        <v>2.1985499835774669</v>
+        <v>2.2012124601419476</v>
       </c>
       <c r="F176" s="0">
-        <v>2.1710696138179988</v>
+        <v>2.166906858741581</v>
       </c>
       <c r="G176" s="0">
-        <v>0.016944168907808397</v>
+        <v>0.0172181413709072</v>
       </c>
       <c r="H176" s="0">
-        <v>-0.0081555608943044474</v>
+        <v>-0.010438156721608508</v>
       </c>
       <c r="I176" s="0">
-        <v>0.0074327127129498252</v>
+        <v>0.013365519006537183</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>2.3926307161251001</v>
+        <v>2.3928247082702598</v>
       </c>
       <c r="B177" s="0">
-        <v>2.1924687637759499</v>
+        <v>2.1912140431094498</v>
       </c>
       <c r="C177" s="0">
-        <v>2.1898182012520802</v>
+        <v>2.1931458917250102</v>
       </c>
       <c r="D177" s="0">
-        <v>2.3735033042598204</v>
+        <v>2.3744107561874923</v>
       </c>
       <c r="E177" s="0">
-        <v>2.197686166518479</v>
+        <v>2.2006433546330251</v>
       </c>
       <c r="F177" s="0">
-        <v>2.1801092574915311</v>
+        <v>2.1757875902223129</v>
       </c>
       <c r="G177" s="0">
-        <v>0.020794734776249383</v>
+        <v>0.019756055551020509</v>
       </c>
       <c r="H177" s="0">
-        <v>-0.0067419298585157271</v>
+        <v>-0.010619065499811413</v>
       </c>
       <c r="I177" s="0">
-        <v>0.0095624584666832366</v>
+        <v>0.016359699524501746</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>2.4073612506834801</v>
+        <v>2.4052631247912899</v>
       </c>
       <c r="B178" s="0">
-        <v>2.18392598314577</v>
+        <v>2.18253881174686</v>
       </c>
       <c r="C178" s="0">
-        <v>2.1963646878126899</v>
+        <v>2.1927371144648098</v>
       </c>
       <c r="D178" s="0">
-        <v>2.3875118133009119</v>
+        <v>2.3884872764335503</v>
       </c>
       <c r="E178" s="0">
-        <v>2.1962500540937109</v>
+        <v>2.1996939709530237</v>
       </c>
       <c r="F178" s="0">
-        <v>2.1890009648613491</v>
+        <v>2.1843593075769041</v>
       </c>
       <c r="G178" s="0">
-        <v>0.018672070317326588</v>
+        <v>0.016358181158380742</v>
       </c>
       <c r="H178" s="0">
-        <v>-0.0084167694800387823</v>
+        <v>-0.012644102607772635</v>
       </c>
       <c r="I178" s="0">
-        <v>0.0069730669916245394</v>
+        <v>0.008779951279928682</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>2.4192891213029601</v>
+        <v>2.4195352302481701</v>
       </c>
       <c r="B179" s="0">
-        <v>2.1973032898750602</v>
+        <v>2.2000136637742398</v>
       </c>
       <c r="C179" s="0">
-        <v>2.2018962809425999</v>
+        <v>2.2002192813103698</v>
       </c>
       <c r="D179" s="0">
-        <v>2.400627860612031</v>
+        <v>2.4016356841889568</v>
       </c>
       <c r="E179" s="0">
-        <v>2.1963630426470471</v>
+        <v>2.2005095706409579</v>
       </c>
       <c r="F179" s="0">
-        <v>2.1981500067890809</v>
+        <v>2.1933928075658731</v>
       </c>
       <c r="G179" s="0">
-        <v>0.018015883748581766</v>
+        <v>0.017263402596085237</v>
       </c>
       <c r="H179" s="0">
-        <v>-0.00045217721956686399</v>
+        <v>-0.0032316063488016379</v>
       </c>
       <c r="I179" s="0">
-        <v>0.0040443520357928307</v>
+        <v>0.0072812863555087931</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>2.4334722379200402</v>
+        <v>2.4351078874256298</v>
       </c>
       <c r="B180" s="0">
-        <v>2.20605931172366</v>
+        <v>2.2058406782752198</v>
       </c>
       <c r="C180" s="0">
-        <v>2.2106168080068098</v>
+        <v>2.2123938985659701</v>
       </c>
       <c r="D180" s="0">
-        <v>2.4139508866894843</v>
+        <v>2.4152530478645917</v>
       </c>
       <c r="E180" s="0">
-        <v>2.1965765517767895</v>
+        <v>2.2010086021288617</v>
       </c>
       <c r="F180" s="0">
-        <v>2.2073370525981373</v>
+        <v>2.202420942019315</v>
       </c>
       <c r="G180" s="0">
-        <v>0.018745075378746527</v>
+        <v>0.018466464978254545</v>
       </c>
       <c r="H180" s="0">
-        <v>0.0099333521115968233</v>
+        <v>0.0057480159970110375</v>
       </c>
       <c r="I180" s="0">
-        <v>0.0034276219110546628</v>
+        <v>0.0099440063964353655</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>2.4502402383451098</v>
+        <v>2.4505546751434402</v>
       </c>
       <c r="B181" s="0">
-        <v>2.2190726232692901</v>
+        <v>2.2180900923036901</v>
       </c>
       <c r="C181" s="0">
-        <v>2.2229857296907301</v>
+        <v>2.2257199322585999</v>
       </c>
       <c r="D181" s="0">
-        <v>2.4270036168622404</v>
+        <v>2.4283931840820459</v>
       </c>
       <c r="E181" s="0">
-        <v>2.1972156916916727</v>
+        <v>2.2020801926916627</v>
       </c>
       <c r="F181" s="0">
-        <v>2.2166291845396771</v>
+        <v>2.211543275966604</v>
       </c>
       <c r="G181" s="0">
-        <v>0.020920406386513459</v>
+        <v>0.019432644030207218</v>
       </c>
       <c r="H181" s="0">
-        <v>0.022731705123925399</v>
+        <v>0.017081691291993557</v>
       </c>
       <c r="I181" s="0">
-        <v>0.0064384238093251915</v>
+        <v>0.013630527749689333</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>2.4624344397002398</v>
+        <v>2.4601518973516798</v>
       </c>
       <c r="B182" s="0">
-        <v>2.2356350270878398</v>
+        <v>2.2342009650950398</v>
       </c>
       <c r="C182" s="0">
-        <v>2.2369942817509898</v>
+        <v>2.2341291047243401</v>
       </c>
       <c r="D182" s="0">
-        <v>2.4393360046730987</v>
+        <v>2.4407755529488053</v>
       </c>
       <c r="E182" s="0">
-        <v>2.1982818500797578</v>
+        <v>2.2037199077438565</v>
       </c>
       <c r="F182" s="0">
-        <v>2.2260529046287494</v>
+        <v>2.2206787012811051</v>
       </c>
       <c r="G182" s="0">
-        <v>0.023328950805582518</v>
+        <v>0.020612848768243805</v>
       </c>
       <c r="H182" s="0">
-        <v>0.036012291341954175</v>
+        <v>0.029809685364103389</v>
       </c>
       <c r="I182" s="0">
-        <v>0.010829313974727311</v>
+        <v>0.013909515386755934</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>2.4762392866730898</v>
+        <v>2.4765236342838</v>
       </c>
       <c r="B183" s="0">
-        <v>2.2425849546660399</v>
+        <v>2.2450003869085098</v>
       </c>
       <c r="C183" s="0">
-        <v>2.24794753968352</v>
+        <v>2.24620193214166</v>
       </c>
       <c r="D183" s="0">
-        <v>2.4518722133963555</v>
+        <v>2.4533844897085002</v>
       </c>
       <c r="E183" s="0">
-        <v>2.1987773773114476</v>
+        <v>2.2049844246200645</v>
       </c>
       <c r="F183" s="0">
-        <v>2.2353128688873358</v>
+        <v>2.2298041649519944</v>
       </c>
       <c r="G183" s="0">
-        <v>0.024061674675442991</v>
+        <v>0.023041938688748119</v>
       </c>
       <c r="H183" s="0">
-        <v>0.044291810150998312</v>
+        <v>0.039204833898480763</v>
       </c>
       <c r="I183" s="0">
-        <v>0.012683232460876622</v>
+        <v>0.016725000868633117</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>2.4871339605825602</v>
+        <v>2.4888092980474901</v>
       </c>
       <c r="B184" s="0">
-        <v>2.24842158554753</v>
+        <v>2.24836767805045</v>
       </c>
       <c r="C184" s="0">
-        <v>2.2584203262025002</v>
+        <v>2.2602233074740701</v>
       </c>
       <c r="D184" s="0">
-        <v>2.4641021249842177</v>
+        <v>2.4659697052087974</v>
       </c>
       <c r="E184" s="0">
-        <v>2.1991429792107349</v>
+        <v>2.2057037027538842</v>
       </c>
       <c r="F184" s="0">
-        <v>2.2445768905752801</v>
+        <v>2.2389124294015854</v>
       </c>
       <c r="G184" s="0">
-        <v>0.023066070661678244</v>
+        <v>0.022594112018298938</v>
       </c>
       <c r="H184" s="0">
-        <v>0.049201010437483782</v>
+        <v>0.042266955171512473</v>
       </c>
       <c r="I184" s="0">
-        <v>0.013862993842838291</v>
+        <v>0.020926132849129534</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>2.4966484188689999</v>
+        <v>2.4970611919229899</v>
       </c>
       <c r="B185" s="0">
-        <v>2.2501950106055602</v>
+        <v>2.2458944711979498</v>
       </c>
       <c r="C185" s="0">
-        <v>2.26812246784695</v>
+        <v>2.2690076960652101</v>
       </c>
       <c r="D185" s="0">
-        <v>2.4762226750245584</v>
+        <v>2.4785105727428132</v>
       </c>
       <c r="E185" s="0">
-        <v>2.1991689265897603</v>
+        <v>2.2060533575609562</v>
       </c>
       <c r="F185" s="0">
-        <v>2.2537971992458319</v>
+        <v>2.2478669618862597</v>
       </c>
       <c r="G185" s="0">
-        <v>0.019837902714094746</v>
+        <v>0.017163154744050221</v>
       </c>
       <c r="H185" s="0">
-        <v>0.050045840313091172</v>
+        <v>0.040706845956850819</v>
       </c>
       <c r="I185" s="0">
-        <v>0.014237056656046847</v>
+        <v>0.020905143618148658</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>2.5007807301004199</v>
+        <v>2.49835624983647</v>
       </c>
       <c r="B186" s="0">
-        <v>2.2445474890725898</v>
+        <v>2.2464994717813198</v>
       </c>
       <c r="C186" s="0">
-        <v>2.2763601317051498</v>
+        <v>2.2753693818593801</v>
       </c>
       <c r="D186" s="0">
-        <v>2.4883468281723604</v>
+        <v>2.490572419344248</v>
       </c>
       <c r="E186" s="0">
-        <v>2.1986778314128732</v>
+        <v>2.2066363726127971</v>
       </c>
       <c r="F186" s="0">
-        <v>2.2629292792053284</v>
+        <v>2.2568464944718194</v>
       </c>
       <c r="G186" s="0">
-        <v>0.013741981798836539</v>
+        <v>0.010088245981129939</v>
       </c>
       <c r="H186" s="0">
-        <v>0.046642908321340541</v>
+        <v>0.039682520636744302</v>
       </c>
       <c r="I186" s="0">
-        <v>0.013645942619182365</v>
+        <v>0.018969258105008522</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>2.5098031939481</v>
+        <v>2.5100941778119901</v>
       </c>
       <c r="B187" s="0"/>
       <c r="C187" s="0">
-        <v>2.2882414938542599</v>
+        <v>2.2865091892326501</v>
       </c>
       <c r="D187" s="0">
-        <v>2.5005100409730439</v>
+        <v>2.5030746375078379</v>
       </c>
       <c r="E187" s="0">
-        <v>2.1982392811374214</v>
+        <v>2.2070821284468347</v>
       </c>
       <c r="F187" s="0">
-        <v>2.2721176880316509</v>
+        <v>2.2658471035849117</v>
       </c>
       <c r="G187" s="0">
-        <v>0.0096187502796611507</v>
+        <v>0.006925033817559159</v>
       </c>
       <c r="H187" s="0">
-        <v>0.044367954962471957</v>
+        <v>0.040076903893866235</v>
       </c>
       <c r="I187" s="0">
-        <v>0.015931147105662641</v>
+        <v>0.020440553894372861</v>
       </c>
     </row>
   </sheetData>
